--- a/PROFORMA_FIYAT_LISTESI.xlsx
+++ b/PROFORMA_FIYAT_LISTESI.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Kalem Detay" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1033</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1097</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3255,8 +3255,620 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" t="n">
+        <v>9</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Kaynak metinde miktar sutunu bos birakilmis (qty=1 varsayildi) ve TOPLAM EURO satiri (line 88) rakam icermiyor - grand total belirtilmemis.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DEPAR MEKANIK A.S.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DM24.10.027</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>45574</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>VRV Klima Sistemi - TPAO Idil Elektrik Binasi</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>83731.81</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>KDV Haric genel toplam. Teklif Icmali sayfasinda 'Montaj Dahil Toplam Fiyat' olarak da 83.731,81 EUR gosteriliyor.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>METRANS Makina Endustrisi Urunleri San. ve Tic. A.S.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>EO2402-TPAO-IDILSITE-COIL</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>TPAO IDIL SITE Crude Oil Transfer Pumps</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" t="n">
+        <v>4</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Bu belge esasen teknik datasheet paketidir; pompalarin ana/baz birim fiyati metinde hic gecmiyor (muhtemelen ayri/dahil edilmemis bir ticari sayfada). Sadece 'Optional Features' (opsiyonel test/kontrol) kalemleri fiyatlandirilmis; genel toplam verilmemis. KULLANICI KONTROL ETMELI.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KROHNE Otomasyon Sanayi ve Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TUMAS Turk Muhendislik - Enstruman Proforma Faturasi</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H72" t="n">
+        <v>8</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TOTAL (KDV haric) = 17.500,00 EUR; VAT %20 = 3.500,00 EUR; grand total 6. arg olarak KDV DAHIL 21.000,00 EUR kullanildi.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>4200.5</v>
+      </c>
+      <c r="H73" t="n">
+        <v>14</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>KDV haric. Kalem toplamlari (4.200,50) basilmis TOPLAM ile birebir uyumlu.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KANCA CRANE Makina Celik Sanayi Ticaret Limited Sirketi</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>KCM 2024/24511</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>10 Ton Gezer Koprulu Vinc Sistemi</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>KDV %20 haric genel toplam. KDV dahil genel toplam 2.520.000 TL (KDV %20 = 420.000 TL) olarak ayrica belirtilmis. Diger alt kalemler (kumanda panosu, elektrik tesisati, kopru imalati vb.) fiyat formunda 0 TL gosterilmis - ana sistem fiyatina dahil kabul edildi.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KANCA CRANE Makina Celik Sanayi Ticaret Limited Sirketi</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KCM 2024/24512</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>30 Ton Gezer Koprulu Vinc Sistemi</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>KDV %20 haric genel toplam. KDV dahil genel toplam 3.780.000 TL (KDV %20 = 630.000 TL) olarak ayrica belirtilmis. Diger alt kalemler 0 TL gosterilmis.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>KANCA CRANE Makina Celik Sanayi Ticaret Limited Sirketi</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>KCM 2024/24512</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>5 Ton Tek Koprulu Gezer Koprulu Vinc Sistemi</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>KDV %20 haric genel toplam. KDV dahil genel toplam 1.620.000 TL (KDV %20 = 270.000 TL) olarak ayrica belirtilmis. Kaynak metinde 'Rerans No' bu teklif icin de KCM 2024/24512 olarak basilmis (30 Ton teklifiyle ayni referans no - kaynak dokumanda muhtemel tekrar/hata, kullanici kontrol etmeli). Diger alt kalemler 0 TL gosterilmis.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KANCA CRANE Makina Celik Sanayi Ticaret Limited Sirketi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>KCM 2024/24512</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2 Ton Tek Koprulu Gezer Koprulu Vinc Sistemi</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>985000</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>KDV %20 haric genel toplam. KDV dahil genel toplam 1.182.000 TL (KDV %20 = 197.000 TL) olarak ayrica belirtilmis. Kaynak metinde 'Rerans No' bu teklif icin de KCM 2024/24512 (once gecen 30 Ton teklifiyle ayni referans no - kaynak dokumanda muhtemel tekrar/hata). Ayrica teknik ozellikler bolumunde 'Kaldirma Kapasitesi (Q): 30 TON' yazili (kopyala-yapistir hatasi olabilir) ama fiyat formu ve konu basligi acikca '2 TON' diyor - 2 Ton olarak kaydedildi. Diger alt kalemler 0 TL gosterilmis.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Entek Teknik Malzeme Enerji Temsilcilik Tic. ve San. A.S.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>45469</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Idil Pompaj Istasyonu PLC Paneli Temini ve Devreye Alinmasi</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Alt Toplam (KDV haric) 500.000 EUR + KDV %20 (100.000 EUR) = Toplam (KDV dahil) 600.000 EUR; grand total 6. arg olarak KDV DAHIL rakam kullanildi.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>3843802.84</v>
+      </c>
+      <c r="H79" t="n">
+        <v>12</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TOPLAM (KDV haric) 3.203.169,03 TL + KDV %20 (640.633,81 TL) = GENEL TOPLAM (KDV dahil) 3.843.802,84 TL; grand total 6. arg olarak KDV DAHIL rakam kullanildi. Kaynak metinde ayrica sifir miktarli/fiyatli bir 'enstruman kablo notu' satiri (13 no) vardi, fiyatlandirilmis kalem olmadigi icin atlandi.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PROMEK Egitim ve Danismanlik Endustri Malzemeleri Insaat Taahhut Ithalat Ihracat Sanayi Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>TUM24/002</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>45570</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Kardan Mafsalli Deprem Kompansatoru Teklifi</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>343005.6</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Fiyatlara KDV dahil degildir (KDV haric).</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RADSAN</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>KR2400000000592</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>40051</v>
+      </c>
+      <c r="H81" t="n">
+        <v>7</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Fiyatlara %20 KDV dahil degildir (KDV haric).</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PROMEK Egitim ve Danismanlik Endustri Malzemeleri Insaat Taahhut Ithalat Ihracat Sanayi Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TUM24/003</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>45582</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Kardan Mafsalli Deprem Kompansatoru Teklifi</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>103860</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Fiyatlara KDV dahil degildir (KDV haric).</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J68"/>
+  <autoFilter ref="A1:J82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3267,7 +3879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1033"/>
+  <dimension ref="A1:L1097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -56760,8 +57372,3336 @@
         </is>
       </c>
     </row>
+    <row r="1034">
+      <c r="A1034" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1034" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>CORTEM EVL-070070 LED Yuksek Tavan Armaturu, 70W, 7.852 Lumen, Ex II 2G Ex db eb op is IIC T4/T5 Gb, IP66</t>
+        </is>
+      </c>
+      <c r="G1034" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1034" s="3" t="n">
+        <v>609.5</v>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1034" s="3" t="n">
+        <v>609.5</v>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="n">
+        <v>1034</v>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1035" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>CORTEM EVL-080100 LED Yuksek Tavan Armaturu, 130W, 12.653 Lumen, Ex II 2G Ex db eb op is IIC T4/T5 Gb, IP66</t>
+        </is>
+      </c>
+      <c r="G1035" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1035" s="3" t="n">
+        <v>825.5</v>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1035" s="3" t="n">
+        <v>825.5</v>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="n">
+        <v>1035</v>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1036" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>CORTEM CSC-216 Exproof Anahtar, 16A, 0-1 Acma/Kapama, EEx d IIC T6, IP66, 2x1" kablo girisli</t>
+        </is>
+      </c>
+      <c r="G1036" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1036" s="3" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1036" s="3" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="n">
+        <v>1036</v>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1037" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>CORTEM SX-26.1 Exproof Buat, EEx d IIC T6, IP66, 4x3/4" kablo girisli</t>
+        </is>
+      </c>
+      <c r="G1037" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1037" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1037" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L1037" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="n">
+        <v>1037</v>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1038" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>CORTEM PY-216B + SPY-216B Exproof Priz-Fis Takimi, 16A, 2P+PE, 220V, EEx d IIC T6, IP66</t>
+        </is>
+      </c>
+      <c r="G1038" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1038" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1038" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="n">
+        <v>1038</v>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1039" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>CORTEM PY-432R + SPY-432R Exproof Priz-Fis Takimi, 16A, 3P+N+PE, 380V, EEx d IIC T6, IP66</t>
+        </is>
+      </c>
+      <c r="G1039" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1039" s="3" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1039" s="3" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="n">
+        <v>1039</v>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1040" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Exproof Start/Stop pushbutonu (kontaklari dahil), 2x1" girisli</t>
+        </is>
+      </c>
+      <c r="G1040" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1040" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1040" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1041" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>CORTEM CSC-R Exproof Acil Stop Butonu, EEx d IIC T6, IP66, 2x1" girisli</t>
+        </is>
+      </c>
+      <c r="G1041" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1041" s="3" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1041" s="3" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="n">
+        <v>1041</v>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>TEKLIF TALEBI (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1042" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>(TPAO) Idil Sirnak Depolama Tesisi TEKLIF TALEBI</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>CORTEM SAG-302318 Ex Terminal Kutusu, montaj plakasi dahil, EEx d IIC T6, IP66, 305x230x190mm</t>
+        </is>
+      </c>
+      <c r="G1042" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1042" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1042" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="n">
+        <v>1042</v>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>DEPAR MEKANIK A.S.</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>DM24.10.027</t>
+        </is>
+      </c>
+      <c r="D1043" s="2" t="n">
+        <v>45574</v>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>VRV Klima Sistemi - TPAO Idil Elektrik Binasi</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>DAIKIN VRV IV Heat Pump C+ Cold Region VRV Klima Sistemi - cihaz paketi (dis uniteler RXYLQ10T/RXYLQ26T, ic uniteler FXZQ/FXFQ serisi, kumandalar, BS-unit vb, 15 kalem)</t>
+        </is>
+      </c>
+      <c r="G1043" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>Paket</t>
+        </is>
+      </c>
+      <c r="I1043" s="3" t="n">
+        <v>62023.56</v>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1043" s="3" t="n">
+        <v>62023.56</v>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="n">
+        <v>1043</v>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>DEPAR MEKANIK A.S.</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>DM24.10.027</t>
+        </is>
+      </c>
+      <c r="D1044" s="2" t="n">
+        <v>45574</v>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>VRV Klima Sistemi - TPAO Idil Elektrik Binasi</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>VRV Klima Sistemi Montaji (bakir boru/izolasyon/joint montaji, ic-dis unite baglantilari, kumanda montaji, azot testi, vakum, gaz sarji, devreye alma)</t>
+        </is>
+      </c>
+      <c r="G1044" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>Paket</t>
+        </is>
+      </c>
+      <c r="I1044" s="3" t="n">
+        <v>21708.25</v>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1044" s="3" t="n">
+        <v>21708.25</v>
+      </c>
+      <c r="L1044" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="n">
+        <v>1044</v>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>METRANS Makina Endustrisi Urunleri San. ve Tic. A.S.</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>EO2402-TPAO-IDILSITE-COIL</t>
+        </is>
+      </c>
+      <c r="D1045" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>TPAO IDIL SITE Crude Oil Transfer Pumps</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Item 1 (340 m3/h - 355m, Model 3600 6x8-14AD, S-6) - Witness unit test with job motor/coupling/baseplate (APIHI-CUT1) opsiyonel ek</t>
+        </is>
+      </c>
+      <c r="G1045" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1045" s="3" t="n">
+        <v>4846.43</v>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1045" s="3" t="n">
+        <v>14539.29</v>
+      </c>
+      <c r="L1045" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="n">
+        <v>1045</v>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>METRANS Makina Endustrisi Urunleri San. ve Tic. A.S.</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>EO2402-TPAO-IDILSITE-COIL</t>
+        </is>
+      </c>
+      <c r="D1046" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>TPAO IDIL SITE Crude Oil Transfer Pumps</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Item 1 (340 m3/h - 355m, Model 3600 6x8-14AD, S-6) - Witnessed mounting pad flatness check on baseplate per API opsiyonel ek</t>
+        </is>
+      </c>
+      <c r="G1046" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1046" s="3" t="n">
+        <v>608.35</v>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1046" s="3" t="n">
+        <v>1825.05</v>
+      </c>
+      <c r="L1046" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>METRANS Makina Endustrisi Urunleri San. ve Tic. A.S.</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>EO2402-TPAO-IDILSITE-COIL</t>
+        </is>
+      </c>
+      <c r="D1047" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>TPAO IDIL SITE Crude Oil Transfer Pumps</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Item 2 (165 m3/h - 355m, Model 3600 4x6-10, S-6) - Witnessed mounting pad flatness check on baseplate per API opsiyonel ek</t>
+        </is>
+      </c>
+      <c r="G1047" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1047" s="3" t="n">
+        <v>538.17</v>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1047" s="3" t="n">
+        <v>1076.34</v>
+      </c>
+      <c r="L1047" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="n">
+        <v>1047</v>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>METRANS Makina Endustrisi Urunleri San. ve Tic. A.S.</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>EO2402-TPAO-IDILSITE-COIL</t>
+        </is>
+      </c>
+      <c r="D1048" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>TPAO IDIL SITE Crude Oil Transfer Pumps</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>Item 2 (165 m3/h - 355m, Model 3600 4x6-10, S-6) - Witness unit test with job motor/coupling/baseplate (APIHI-CUT1) opsiyonel ek</t>
+        </is>
+      </c>
+      <c r="G1048" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1048" s="3" t="n">
+        <v>4846.43</v>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1048" s="3" t="n">
+        <v>9692.860000000001</v>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="n">
+        <v>1048</v>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>KROHNE Otomasyon Sanayi ve Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1049" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>TUMAS Turk Muhendislik - Enstruman Proforma Faturasi</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>Pressure Ind. Transmitter</t>
+        </is>
+      </c>
+      <c r="G1049" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1049" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1049" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="n">
+        <v>1049</v>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>KROHNE Otomasyon Sanayi ve Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1050" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>TUMAS Turk Muhendislik - Enstruman Proforma Faturasi</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>Pressure Indicator</t>
+        </is>
+      </c>
+      <c r="G1050" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1050" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1050" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="L1050" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>KROHNE Otomasyon Sanayi ve Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1051" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>TUMAS Turk Muhendislik - Enstruman Proforma Faturasi</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Temperature Indicator</t>
+        </is>
+      </c>
+      <c r="G1051" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1051" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1051" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="n">
+        <v>1051</v>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>KROHNE Otomasyon Sanayi ve Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1052" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>TUMAS Turk Muhendislik - Enstruman Proforma Faturasi</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Level Switch</t>
+        </is>
+      </c>
+      <c r="G1052" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1052" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1052" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="n">
+        <v>1052</v>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>KROHNE Otomasyon Sanayi ve Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1053" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>TUMAS Turk Muhendislik - Enstruman Proforma Faturasi</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>Diff. Pressure Indicator</t>
+        </is>
+      </c>
+      <c r="G1053" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1053" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1053" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>KROHNE Otomasyon Sanayi ve Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1054" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>TUMAS Turk Muhendislik - Enstruman Proforma Faturasi</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>Temp. Ind. Transmitter</t>
+        </is>
+      </c>
+      <c r="G1054" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1054" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1054" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L1054" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>KROHNE Otomasyon Sanayi ve Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1055" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>TUMAS Turk Muhendislik - Enstruman Proforma Faturasi</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Flow Switch</t>
+        </is>
+      </c>
+      <c r="G1055" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1055" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1055" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>KROHNE Otomasyon Sanayi ve Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1056" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>TUMAS Turk Muhendislik - Enstruman Proforma Faturasi</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Level Indicator</t>
+        </is>
+      </c>
+      <c r="G1056" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1056" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1056" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="L1056" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="n">
+        <v>1056</v>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1057" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>CORTEM FLOWEX-080070 LED Armatur, 70W, 9.547 lm, IP66, 5000K, Ex db eb mb IIC T5/86C, Zone 1/21</t>
+        </is>
+      </c>
+      <c r="G1057" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1057" s="3" t="n">
+        <v>609.7</v>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1057" s="3" t="n">
+        <v>609.7</v>
+      </c>
+      <c r="L1057" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="n">
+        <v>1057</v>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1058" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>CORTEM CSCD-216 vaviyen 1-2 Anahtar, 16A, Ex db IIC T6, IP66, Zone 1/21</t>
+        </is>
+      </c>
+      <c r="G1058" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1058" s="3" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1058" s="3" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="L1058" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1059" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>CORTEM LIFEX-ME-1230N Acil Aydinlatma Armaturu, Lineer LED 30W 4.112lm, Ni-Cd batarya 180dk, IP66, Zone1/21</t>
+        </is>
+      </c>
+      <c r="G1059" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1059" s="3" t="n">
+        <v>490.1</v>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1059" s="3" t="n">
+        <v>490.1</v>
+      </c>
+      <c r="L1059" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="n">
+        <v>1059</v>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1060" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>CORTEM CSC-216 normal anahtar, 16A, Ex db IIC T6, IP66, Zone 1/21</t>
+        </is>
+      </c>
+      <c r="G1060" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1060" s="3" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1060" s="3" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="L1060" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1061" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>CORTEM ST-26.1 buat, 3x3/4" girisli, Exd IIC Gb, IP66, Zone 1/21</t>
+        </is>
+      </c>
+      <c r="G1061" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1061" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1061" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L1061" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="n">
+        <v>1061</v>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1062" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>CORTEM SL-26.1 buat, 2x3/4" girisli, Exd IIC Gb, IP66, Zone 1/21</t>
+        </is>
+      </c>
+      <c r="G1062" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1062" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1062" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L1062" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="n">
+        <v>1062</v>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1063" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>CORTEM ELF-2 3/4" dirsek, Ex db IIC Gb, IP66/67, Zone 1/2</t>
+        </is>
+      </c>
+      <c r="G1063" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1063" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1063" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L1063" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="n">
+        <v>1063</v>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1064" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>CORTEM EYS-2 3/4" Durdurucu, Ex db IIC Gb, IP66/67, Zone 1/2</t>
+        </is>
+      </c>
+      <c r="G1064" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1064" s="3" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1064" s="3" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="L1064" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="n">
+        <v>1064</v>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1065" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>CORTEM EM-2 3/4" mansson, Ex db IIB Gb, IP66/67, Zone 1/2</t>
+        </is>
+      </c>
+      <c r="G1065" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1065" s="3" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1065" s="3" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="L1065" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="n">
+        <v>1065</v>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1066" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>CORTEM PY-216B 16A Monofaze priz ve fis, Ex d IIC T6 Gb, Zone 1/2</t>
+        </is>
+      </c>
+      <c r="G1066" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1066" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1066" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="L1066" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="n">
+        <v>1066</v>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1067" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>CORTEM PY-432R 16A Trifaze priz ve fis, Ex d IIC T6 Gb, Zone 1/2</t>
+        </is>
+      </c>
+      <c r="G1067" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1067" s="3" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1067" s="3" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="L1067" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="n">
+        <v>1067</v>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1068" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>CORTEM BMF-2 3/4" uc parcali rekor erkek-disi, Ex db IIB Gb, IP66/67, Zone 1/2</t>
+        </is>
+      </c>
+      <c r="G1068" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1068" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1068" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1068" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="n">
+        <v>1068</v>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1069" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>CORTEM LBHS-2 3/4" kapakli dirsek, Ex d IIB, IP66, Zone 1/21</t>
+        </is>
+      </c>
+      <c r="G1069" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1069" s="3" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1069" s="3" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="L1069" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="n">
+        <v>1069</v>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>ELPIM Muhendislik Musavirlik Elektrik San. ve Tic. Ltd. Sti</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>TEKLIF (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1070" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>TPAO Idil Sirnak Depolama Tesisi</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>FITRE TASS22 AD Telefon, Ex e mb (ib) IIC T5, IP66</t>
+        </is>
+      </c>
+      <c r="G1070" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1070" s="3" t="n">
+        <v>2198</v>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1070" s="3" t="n">
+        <v>2198</v>
+      </c>
+      <c r="L1070" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>KANCA CRANE Makina Celik Sanayi Ticaret Limited Sirketi</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>KCM 2024/24511</t>
+        </is>
+      </c>
+      <c r="D1071" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>10 Ton Gezer Koprulu Vinc Sistemi</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>10 Ton cift kiris tipi gezer koprulu tavan vinc sistemi (kaldirma grubu, kumanda panosu, kopru basligi, elektrik tesisati dahil komple sistem)</t>
+        </is>
+      </c>
+      <c r="G1071" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1071" s="3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1071" s="3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="L1071" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="n">
+        <v>1071</v>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>KANCA CRANE Makina Celik Sanayi Ticaret Limited Sirketi</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>KCM 2024/24512</t>
+        </is>
+      </c>
+      <c r="D1072" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>30 Ton Gezer Koprulu Vinc Sistemi</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>30 Ton cift kiris tipi gezer koprulu tavan vinc sistemi (kaldirma grubu, kumanda panosu, kopru basligi, elektrik tesisati dahil komple sistem)</t>
+        </is>
+      </c>
+      <c r="G1072" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1072" s="3" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1072" s="3" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="L1072" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="n">
+        <v>1072</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>KANCA CRANE Makina Celik Sanayi Ticaret Limited Sirketi</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>KCM 2024/24512</t>
+        </is>
+      </c>
+      <c r="D1073" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>5 Ton Tek Koprulu Gezer Koprulu Vinc Sistemi</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>5 Ton tek kiris tipi gezer koprulu tavan vinc sistemi (kaldirma grubu, kumanda panosu, kopru basligi, elektrik tesisati dahil komple sistem)</t>
+        </is>
+      </c>
+      <c r="G1073" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1073" s="3" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1073" s="3" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L1073" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="n">
+        <v>1073</v>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>KANCA CRANE Makina Celik Sanayi Ticaret Limited Sirketi</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>KCM 2024/24512</t>
+        </is>
+      </c>
+      <c r="D1074" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>2 Ton Tek Koprulu Gezer Koprulu Vinc Sistemi</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>2 Ton tek kiris tipi gezer koprulu tavan vinc sistemi (kaldirma grubu, kumanda panosu, kopru basligi, elektrik tesisati dahil komple sistem)</t>
+        </is>
+      </c>
+      <c r="G1074" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1074" s="3" t="n">
+        <v>985000</v>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1074" s="3" t="n">
+        <v>985000</v>
+      </c>
+      <c r="L1074" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="n">
+        <v>1074</v>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Entek Teknik Malzeme Enerji Temsilcilik Tic. ve San. A.S.</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>PROFORMA FATURA (Ref yok)</t>
+        </is>
+      </c>
+      <c r="D1075" s="2" t="n">
+        <v>45469</v>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>Idil Pompaj Istasyonu PLC Paneli Temini ve Devreye Alinmasi</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Idil Pompaj Istasyonu PLC Paneli Temini ve Devreye Alinmasi (10 adet Pompa PLC Sistemi, CPU, haberlesme/network kartlari, 10" HMI, IS bariyerleri, pano ici baglantilar, yazilim ve lisanslar dahil)</t>
+        </is>
+      </c>
+      <c r="G1075" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1075" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1075" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L1075" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="n">
+        <v>1075</v>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1076" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl BLACK 1x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1076" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1076" s="3" t="n">
+        <v>49.4349</v>
+      </c>
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1076" s="3" t="n">
+        <v>49434.9</v>
+      </c>
+      <c r="L1076" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="n">
+        <v>1076</v>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1077" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl PIMF BLACK 2x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1077" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1077" s="3" t="n">
+        <v>93.54519999999999</v>
+      </c>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1077" s="3" t="n">
+        <v>93545.2</v>
+      </c>
+      <c r="L1077" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="n">
+        <v>1077</v>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1078" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl PIMF BLACK 4x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1078" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1078" s="3" t="n">
+        <v>138.9711</v>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1078" s="3" t="n">
+        <v>138971.1</v>
+      </c>
+      <c r="L1078" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="n">
+        <v>1078</v>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1079" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl PIMF BLACK 6x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1079" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1079" s="3" t="n">
+        <v>212.1013</v>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1079" s="3" t="n">
+        <v>212101.3</v>
+      </c>
+      <c r="L1079" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="n">
+        <v>1079</v>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1080" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl PIMF BLACK 8x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1080" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1080" s="3" t="n">
+        <v>255.2821</v>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1080" s="3" t="n">
+        <v>255282.1</v>
+      </c>
+      <c r="L1080" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1081" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl PIMF BLACK 10x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1081" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1081" s="3" t="n">
+        <v>314.7587</v>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1081" s="3" t="n">
+        <v>314758.7</v>
+      </c>
+      <c r="L1081" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1082" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl PIMF BLACK 12x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1082" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1082" s="3" t="n">
+        <v>365.0258</v>
+      </c>
+      <c r="J1082" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1082" s="3" t="n">
+        <v>365025.8</v>
+      </c>
+      <c r="L1082" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="n">
+        <v>1082</v>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1083" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl PIMF BLACK 16x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1083" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1083" s="3" t="n">
+        <v>477.8021</v>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1083" s="3" t="n">
+        <v>477802.1</v>
+      </c>
+      <c r="L1083" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="n">
+        <v>1083</v>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1084" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl PIMF BLACK 20x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1084" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1084" s="3" t="n">
+        <v>590.9489</v>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1084" s="3" t="n">
+        <v>590948.9</v>
+      </c>
+      <c r="L1084" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="n">
+        <v>1084</v>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1085" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl PIMF BLACK 24x2x1,5 mm2 EN 50288-7 500V 70C RAL 9005 Black</t>
+        </is>
+      </c>
+      <c r="G1085" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1085" s="3" t="n">
+        <v>698.4758</v>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1085" s="3" t="n">
+        <v>698475.8</v>
+      </c>
+      <c r="L1085" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="n">
+        <v>1085</v>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1086" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>LI2Y(St)CH-PF 2x2x24 AWG RS 485 modbus (%65 TC/SNCU orgu kapama), RAL 7001 Gri</t>
+        </is>
+      </c>
+      <c r="G1086" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1086" s="3" t="n">
+        <v>26.333</v>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1086" s="3" t="n">
+        <v>2633.3</v>
+      </c>
+      <c r="L1086" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="n">
+        <v>1086</v>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>ETA Birkablo (marka: BIRTAS KABLO)</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>202402762</t>
+        </is>
+      </c>
+      <c r="D1087" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>TPAO Sirnak Idil Sahasi Pompaj Istasyonu ve Ham Petrol Depolama Tesisi - Kablo Teklifi</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>LI-O2YS(St)CY 1x2x18/1AWG PROFIBUS PA, RAL 5015 Mavi</t>
+        </is>
+      </c>
+      <c r="G1087" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1087" s="3" t="n">
+        <v>41.8983</v>
+      </c>
+      <c r="J1087" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1087" s="3" t="n">
+        <v>4189.83</v>
+      </c>
+      <c r="L1087" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>PROMEK Egitim ve Danismanlik Endustri Malzemeleri Insaat Taahhut Ithalat Ihracat Sanayi Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>TUM24/002</t>
+        </is>
+      </c>
+      <c r="D1088" s="2" t="n">
+        <v>45570</v>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>Kardan Mafsalli Deprem Kompansatoru Teklifi</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>RT7200600-F PN16 Kardan Mafsalli Deprem Kompansatoru Flansli, DN600, L:1370mm, AISI304 korukli, St37-2 govde</t>
+        </is>
+      </c>
+      <c r="G1088" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1088" s="3" t="n">
+        <v>138146.4</v>
+      </c>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1088" s="3" t="n">
+        <v>138146.4</v>
+      </c>
+      <c r="L1088" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="n">
+        <v>1088</v>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>PROMEK Egitim ve Danismanlik Endustri Malzemeleri Insaat Taahhut Ithalat Ihracat Sanayi Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>TUM24/002</t>
+        </is>
+      </c>
+      <c r="D1089" s="2" t="n">
+        <v>45570</v>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>Kardan Mafsalli Deprem Kompansatoru Teklifi</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>RT7200750-F PN16 Kardan Mafsalli Deprem Kompansatoru Flansli, DN750, L:1370mm, AISI304 korukli, St37-2 govde</t>
+        </is>
+      </c>
+      <c r="G1089" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1089" s="3" t="n">
+        <v>204859.2</v>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1089" s="3" t="n">
+        <v>204859.2</v>
+      </c>
+      <c r="L1089" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="n">
+        <v>1089</v>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>RADSAN</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>KR2400000000592</t>
+        </is>
+      </c>
+      <c r="D1090" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>MH-08.06.D2 35 mm2 Galvaniz Monotron Iletken tel (7,65 mm)</t>
+        </is>
+      </c>
+      <c r="G1090" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1090" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1090" s="3" t="n">
+        <v>2550</v>
+      </c>
+      <c r="L1090" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="n">
+        <v>1090</v>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>RADSAN</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>KR2400000000592</t>
+        </is>
+      </c>
+      <c r="D1091" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>CG-101.13.D 50 mikron Sicak galvaniz kapli serit, 40x4mm</t>
+        </is>
+      </c>
+      <c r="G1091" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="I1091" s="3" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1091" s="3" t="n">
+        <v>4901</v>
+      </c>
+      <c r="L1091" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="n">
+        <v>1091</v>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>RADSAN</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>KR2400000000592</t>
+        </is>
+      </c>
+      <c r="D1092" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>NYAF-101.05 16 mm2 NYAF Kablo, sari-yesil</t>
+        </is>
+      </c>
+      <c r="G1092" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1092" s="3" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1092" s="3" t="n">
+        <v>7050</v>
+      </c>
+      <c r="L1092" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="n">
+        <v>1092</v>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>RADSAN</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>KR2400000000592</t>
+        </is>
+      </c>
+      <c r="D1093" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>NYAF-101.08 50 mm2 NYAF Kablo, sari-yesil</t>
+        </is>
+      </c>
+      <c r="G1093" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1093" s="3" t="n">
+        <v>218.35</v>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1093" s="3" t="n">
+        <v>21835</v>
+      </c>
+      <c r="L1093" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="n">
+        <v>1093</v>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>RADSAN</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>KR2400000000592</t>
+        </is>
+      </c>
+      <c r="D1094" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>RIP.101.01 Topraklama Rogari, 50x60x60 cm, Beton</t>
+        </is>
+      </c>
+      <c r="G1094" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1094" s="3" t="n">
+        <v>2650</v>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1094" s="3" t="n">
+        <v>2650</v>
+      </c>
+      <c r="L1094" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="n">
+        <v>1094</v>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>RADSAN</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>KR2400000000592</t>
+        </is>
+      </c>
+      <c r="D1095" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>EBK.200.02 40x5x300 mm Espotansiyel Bara, Izolatorlu, Sicak galvaniz</t>
+        </is>
+      </c>
+      <c r="G1095" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1095" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1095" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="L1095" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="n">
+        <v>1095</v>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>RADSAN</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>KR2400000000592</t>
+        </is>
+      </c>
+      <c r="D1096" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>ELT.104.01 25x25cm Statik Bakir Levha 1mm (TR)</t>
+        </is>
+      </c>
+      <c r="G1096" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1096" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1096" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="L1096" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="n">
+        <v>1096</v>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>PROMEK Egitim ve Danismanlik Endustri Malzemeleri Insaat Taahhut Ithalat Ihracat Sanayi Ticaret Ltd. Sti.</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>TUM24/003</t>
+        </is>
+      </c>
+      <c r="D1097" s="2" t="n">
+        <v>45582</v>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>Kardan Mafsalli Deprem Kompansatoru Teklifi</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>RT7200400-F PN16 Kardan Mafsalli Deprem Kompansatoru Flansli, DN400, L:1400mm, Class150, AISI304 korukli, St37-2 govde</t>
+        </is>
+      </c>
+      <c r="G1097" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1097" s="3" t="n">
+        <v>103860</v>
+      </c>
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1097" s="3" t="n">
+        <v>103860</v>
+      </c>
+      <c r="L1097" t="inlineStr">
+        <is>
+          <t>1393A_313480kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1033"/>
+  <autoFilter ref="A1:L1097"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/PROFORMA_FIYAT_LISTESI.xlsx
+++ b/PROFORMA_FIYAT_LISTESI.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Kalem Detay" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1097</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3867,8 +3867,52 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>TL (KDV Dahil)</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>381207.07</v>
+      </c>
+      <c r="H83" t="n">
+        <v>15</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Ara Toplam/Brüt Toplam (KDV Hariç) 317.672,56 TL + KDV %20 63.534,51 TL = Genel Toplam 381.207,07 TL</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J82"/>
+  <autoFilter ref="A1:J83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3879,7 +3923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1097"/>
+  <dimension ref="A1:L1112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -60700,8 +60744,788 @@
         </is>
       </c>
     </row>
+    <row r="1098">
+      <c r="A1098" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1098" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>K200KM8 - 200mm PE SN8 Perforeli Triplex Kanal Borusu</t>
+        </is>
+      </c>
+      <c r="G1098" s="4" t="n">
+        <v>644</v>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1098" s="3" t="n">
+        <v>181.24</v>
+      </c>
+      <c r="J1098" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1098" s="3" t="n">
+        <v>116718.56</v>
+      </c>
+      <c r="L1098" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="n">
+        <v>1098</v>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1099" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>K200M - 200mm PE Triplex Boru Manşon</t>
+        </is>
+      </c>
+      <c r="G1099" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1099" s="3" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="J1099" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1099" s="3" t="n">
+        <v>5566</v>
+      </c>
+      <c r="L1099" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="n">
+        <v>1099</v>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1100" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>K200C - 200mm Triplex Muflu Boru Conta</t>
+        </is>
+      </c>
+      <c r="G1100" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1100" s="3" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="J1100" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1100" s="3" t="n">
+        <v>3453.68</v>
+      </c>
+      <c r="L1100" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1101" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>K200KM8 - 200mm PE SN8 Triplex Muflu Boru</t>
+        </is>
+      </c>
+      <c r="G1101" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1101" s="3" t="n">
+        <v>168.94</v>
+      </c>
+      <c r="J1101" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1101" s="3" t="n">
+        <v>20272.8</v>
+      </c>
+      <c r="L1101" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1102" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>K300KM8 - 300mm PE SN8 Perforeli Triplex Kanal Borusu</t>
+        </is>
+      </c>
+      <c r="G1102" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1102" s="3" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="J1102" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1102" s="3" t="n">
+        <v>16029.3</v>
+      </c>
+      <c r="L1102" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1103" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>K300M - 300mm PE Triplex Boru Manşon</t>
+        </is>
+      </c>
+      <c r="G1103" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1103" s="3" t="n">
+        <v>140.88</v>
+      </c>
+      <c r="J1103" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1103" s="3" t="n">
+        <v>845.28</v>
+      </c>
+      <c r="L1103" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1104" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>K300C - 300mm Triplex Muflu Ek Parça Contası</t>
+        </is>
+      </c>
+      <c r="G1104" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1104" s="3" t="n">
+        <v>120.47</v>
+      </c>
+      <c r="J1104" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1104" s="3" t="n">
+        <v>1445.64</v>
+      </c>
+      <c r="L1104" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1105" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>YDK - 200mm PE Triplex T Çatal 90</t>
+        </is>
+      </c>
+      <c r="G1105" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1105" s="3" t="n">
+        <v>262.65</v>
+      </c>
+      <c r="J1105" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1105" s="3" t="n">
+        <v>2889.15</v>
+      </c>
+      <c r="L1105" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1106" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>K20045D - 200mm PE Triplex Boru Dirsek (45°)</t>
+        </is>
+      </c>
+      <c r="G1106" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1106" s="3" t="n">
+        <v>119.97</v>
+      </c>
+      <c r="J1106" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1106" s="3" t="n">
+        <v>2999.25</v>
+      </c>
+      <c r="L1106" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1107" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>K20090D - 200mm PE Triplex Boru Dirsek (90°)</t>
+        </is>
+      </c>
+      <c r="G1107" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1107" s="3" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="J1107" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1107" s="3" t="n">
+        <v>3393.5</v>
+      </c>
+      <c r="L1107" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1108" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>K100KM8 - 100mm PE SN8 Triplex Muflu Boru</t>
+        </is>
+      </c>
+      <c r="G1108" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1108" s="3" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="J1108" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1108" s="3" t="n">
+        <v>9550.860000000001</v>
+      </c>
+      <c r="L1108" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1109" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>k100km8 - 100mm PE SN8 Triplex Muflu Boru</t>
+        </is>
+      </c>
+      <c r="G1109" s="4" t="n">
+        <v>660</v>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1109" s="3" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="J1109" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1109" s="3" t="n">
+        <v>36227.4</v>
+      </c>
+      <c r="L1109" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1110" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>k100km8 - 100mm PE SN8 Triplex Muflu Boru</t>
+        </is>
+      </c>
+      <c r="G1110" s="4" t="n">
+        <v>702</v>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1110" s="3" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="J1110" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1110" s="3" t="n">
+        <v>38532.78</v>
+      </c>
+      <c r="L1110" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1111" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>k100km8 - 100mm PE SN8 Triplex Muflu Boru</t>
+        </is>
+      </c>
+      <c r="G1111" s="4" t="n">
+        <v>924</v>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1111" s="3" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1111" s="3" t="n">
+        <v>50718.36</v>
+      </c>
+      <c r="L1111" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>ÖZDOĞANPLAST PLASTİK VE KİM.MAD.PAZ.SAN.VE TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>TKF202600001267</t>
+        </is>
+      </c>
+      <c r="D1112" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>Genel Malzeme Talebi (PE Triplex Boru/Kanal Sistemi)</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>k150km8 - 150mm PE SN8 Triplex Muflu Boru</t>
+        </is>
+      </c>
+      <c r="G1112" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1112" s="3" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="J1112" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1112" s="3" t="n">
+        <v>9030</v>
+      </c>
+      <c r="L1112" t="inlineStr">
+        <is>
+          <t>ozdoganplast.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1097"/>
+  <autoFilter ref="A1:L1112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/PROFORMA_FIYAT_LISTESI.xlsx
+++ b/PROFORMA_FIYAT_LISTESI.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Kalem Detay" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1269</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3911,8 +3911,1104 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>192850</v>
+      </c>
+      <c r="H84" t="n">
+        <v>11</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>KDV dahil değildir; recipient HB Elektrik</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>246301.2</v>
+      </c>
+      <c r="H85" t="n">
+        <v>10</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sayfa toplamı 205.251,00 TL + KDV %20 41.050,20 TL = Genel 246.301,20 TL. 7 ve 8 nolu kalemler Ankara teslimi, diğerleri G.Antep fabrika teslimi.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CONSOLE OTOMASYON</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>T21-0825-PGO1_Rev0</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu PLC Teklifi</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>61920</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Toplam Tutar (KDV hariç) 51.600 EUR + KDV %20 = 61.920 EUR (KDV dahil). Ödeme: 30 gün, %100 malzeme teslimi.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>3063.92</v>
+      </c>
+      <c r="H87" t="n">
+        <v>15</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Toplam EURO 2.553,27 + %20 KDV 510,65 = Genel Toplam 3.063,92 EUR. Teslim yeri İzmir depoları.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>80586.92999999999</v>
+      </c>
+      <c r="H88" t="n">
+        <v>16</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Toplam Tutar (KDV hariç) $73.594,29 + KDV(%10 tevkifatlı) $6.992,63 + KDV(%20) $733,59 = G. Toplam $80.586,93. NOT: farklı Teklif Ref No/tutar - FB1712-12110 ($142.822,80/$171.387,37) bilinen bir duplike olarak atlandı, bu FB1712-12089 farklı ve yeni bir tekliftir.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Arde Aydınlatma (Detay Aydınlatma)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>7148</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Yol Aydınlatma Armatürü Teklifi (Firma: HB Elektrik Proje ve Müşavirlik)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>1512</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>KDV Hariç Toplam 1.260,00 USD + KDV 252,00 USD = Genel Toplam 1.512,00 USD</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ETE Enerji Tesisleri Endüstrisi Sanayi Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ref yok (13.06.2026 teklifi)</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ex-Proof Elektrik Malzemeleri (Firma: Key Oil &amp; Gas, İlgili: Melih Serindere)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>1217.23</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Toplam 1.014,36 EUR + KDV 202,87 EUR = Genel Toplam 1.217,23 EUR. Teslim: Ankara Depo, 8-10 hafta.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>VISVANA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>T1-264106</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Çamur Kutusu Teklifi (Şirket: KEYOİLGAS)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>6544.41</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Yükleme yeri Vis Fabrika, ödeme nakit</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EAE Elektrik Aydınlatma Endüstrisi San. ve Tic. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>11502376 Rev.0</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Şırnak Endüstriyel Tesis Aydınlatma Teklifi (Firma: Hb Elektrik Prj.Müş.San.Ve Tic.Ltd., Proje No: PA-0000040)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>7704.31</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Ara Toplam 6.420,26 USD + KDV %20 1.284,05 USD = Genel Toplam 7.704,31 USD. Kaynak dosyada bu teklif 'PROFORMA FATURA' (7 sayfa) ve 'TEKLİF MEKTUBU' (5 sayfa) başlıkları altında AYNI içerikle iki kez basılmış; sadece bir kez sayıldı.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>35789.5</v>
+      </c>
+      <c r="H93" t="n">
+        <v>23</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>BELİRSİZ: Vendor adı bu sayfada basılı değil. Aynı tarihte (8.05.2026) S NOVAGROUP/YILKOMER TL teklifiyle (REF 20251209-2) örtüşen kalemler içeriyor ancak daha geniş kapsamlı (Topraklama Sistemi dahil) ve USD cinsinden. Aynı tekrarlanan tekliflerin bir varyasyonu/genişletilmiş hali olabilir - lütfen ana listeye eklerken bu ihtimali değerlendirin.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Yaman Endüstriyel Otomasyon (Bülent Gürkanlı)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-06-09-001-KEY-R00</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>TPAO Mehmet İrfan Güler Petrol Üretim İstasyonu Detay Mühendislik İşi - PLC Teklifi</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>63500</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Vendor toplu tek bir toplam satırı basmamış; 57.500 EUR (PLC) + 6.000 EUR (devreye alma) kalemlerinden hesaplandı. KDV hariç. Fazla mesai saatlik 150 EUR.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Burçelik Vana San. ve Tic. A.Ş. (Burcelik Valve)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AE26210 R0</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu Detay Mühendislik İşi - Vana Paketi</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>239697.3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Incoterms EXW-Bursa/Türkiye, ödeme %50 avans, teslim 12-14 hafta, garanti 2 yıl</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ELSU BORU ELEKTRİK PLASTİK İNŞ. TAAH. PAZ. NAK. SAN. TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>T2605-00705</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Şırnak TPAO Mehmet İrfan Güler - 6 Inch Pompaj Hattı Yapım İşi (Koruge Boru)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>86000.88</v>
+      </c>
+      <c r="H96" t="n">
+        <v>5</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Toplam 71.667,40 TL - İndirim 0,00 + KDV 14.333,48 = Net Toplam 86.000,88 TL. 3 adet manşon kalemi (Ø50/Ø75/Ø110mm manşon) 0,00 TL fiyatla listelenmiş, atlandı. Teslim: Kayseri fabrika, kredi kartı ödeme.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Endress+Hauser Elektronik Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2051095090 (Bütçesel Teklif)</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Referans - Basınç/Sıcaklık/Seviye Enstrümantasyonu</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>24516.84</v>
+      </c>
+      <c r="H97" t="n">
+        <v>5</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Toplam fiyat 20.375,88 + Kargo 54,82 = Net değer 20.430,70 + KDV%20 4.086,14 = KDV dahil Toplam 24.516,84 EUR. Teslim DAP Kartal Incoterms 2020, %25 avans %75 teslimden önce.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Bilinmeyen (Ref. Kod: FA26060801)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FA26060801</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak Projesi - Yangın Hidrant Sistemi Malzemeleri</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>29275.91</v>
+      </c>
+      <c r="H98" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>BELİRSİZ: Vendor logosu/adı OCR'de kayıp, sadece 'Firma:' alanı KEY OIL AND GAS (alıcı) gösteriyor. Ref Kodu 'FA26060801' (R1 eki YOK) - listede zaten bulunan 'FA26060801R1' (30.657,31 USD) teklifinin muhtemel bir önceki revizyonu/R0'ı olabilir; tutar da farklı (29.275,91 USD). Aynı proje/tedarikçiye ait olası revizyon çifti olarak değerlendirilmeli.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SCHNEIDER ELEKTRİK SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PRF11052026.2</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Proforma Fatura (Bütçelendirme Teklifi) - Şırnak Endüstriyel Tesis (Müşteri: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>41500</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>KDV ilave edilecektir. Ödeme %30 avans, bakiye fatura mukabili 15 gün. Fiyatlar EXW Partner teslim.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ARLIGHT AYDINLATMA A.Ş.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Proje Kodu 2026011437 / Referans SO26735</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Şırnak Endüstriyel Tesis Projesi Aydınlatma Teklifi (Müşteri: Hb Elektrik Proje ve Müşavirlik)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>4375.02</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Toplam 3.645,85 EUR + KDV%20 729,17 EUR = Genel Toplam 4.375,02 EUR</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MANFRED GELDBACH</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ST26-003951 Rev.1</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Bağlantı Elemanları</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>3690.02</v>
+      </c>
+      <c r="H101" t="n">
+        <v>7</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>KDV Hariç Toplam 3.075,02 EUR + KDV 615,00 EUR = KDV Dahil Tutar 3.690,02 EUR. Ürünler MG markalı, teslim depo/stok. Kaynak dosyada bu teklif iki kez (aynı içerikle) basılmış; bir kez sayıldı.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>VALFTEK</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>26-0215</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Küresel Vana Talebi (LF2/S355J2 gövde, RPTFE grafit sızdırmazlık, AISI316 küre/mil, üç parçalı tam geçişli dişli)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>1798.8</v>
+      </c>
+      <c r="H102" t="n">
+        <v>8</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Vendor tarafından basılı bir genel toplam satırı yok; 1.798,80 EUR kalemlerin toplamından hesaplandı. Teslim Kocaeli ambar, opsiyon 7 gün.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AKEL BORU SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>S101534</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Talebi (Müşteri: KEY OİL GAS)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>64392.66</v>
+      </c>
+      <c r="H103" t="n">
+        <v>6</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Genel Toplam: 25.502,72 kg / 64.392,66 EUR. Farklı bir teklif no (S101830 zaten listede bilinen bir duplike; bu S101534 yeni ve farklı). Kaynak dosyada bu teklif iki kez (aynı içerikle) basılmış; bir kez sayıldı.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>33240.9</v>
+      </c>
+      <c r="H104" t="n">
+        <v>16</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Toplam 33.240,90 USD - İnd.Toplamı 0,00 = İndirimli Toplam 33.240,90 USD (KDV hariç, %20 KDV ayrıca ilave edilecek). Teslim Des Depomuz, 7-10 iş günü.</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>DZA MÜHENDİSLİK - Ömer Ulukan Reşitoğlu</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>260622-024</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Ham Petrol Üretim İstasyonu - Zemin Çivisi Yapım İşi</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>6336000</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Ara Toplam 5.580.000,00 TL + KDV%20 1.056.000,00 TL = Genel Toplam 6.336.000,00 TL. Geçerlilik 30 gün.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Hacı Ayvaz Endüstriyel Mamüller Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>STT0151405</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Yangın Hidrantı ve Vana Teklifi</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Karma (TL 28.357,00 + USD 1.043,00)</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n"/>
+      <c r="H106" t="n">
+        <v>4</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>KDV Hariç Toplam TL 28.357,00 ve KDV Hariç Toplam USD 1.043,00 ayrı ayrı verilmiş (karma para birimi). Liste fiyatı üzerinden %65 iskonto uygulanmış. Ödeme %100 peşin, teslim Hadımköy depo.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Bilinmeyen (muhtemelen Klinger Turkey sevkiyatına ait iç taşıma maliyeti hesabı)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ref yok - Demir Profil ve Sac Taşıma Birim Fiyatı Tespiti</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Ereğli OSB - Şırnak MIG Proje Şantiyesi Nakliye Bedeli Hesabı</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>4431.11</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>BELİRSİZ: Bu sayfada vendor adı/logosu yok; Klinger Turkey teklifinin (825-290426-KD, bilinen duplike) hemen ardından gelen ayrı bir sayfa - muhtemelen o sevkiyata ait iç/harici bir taşıma maliyeti hesap kağıdı, klasik bir 'teklif' formatında değil (formül bazlı hesap: F=Kx(0,0007xM+0,01)xA). Taşıma bedeli 3.658,43 TL/TON + yükleme-boşaltma yarısı 113,54 (toplam formülde 3.544,89 gösteriliyor, küçük yuvarlama farkı var) + %25 kar = Genel Toplam 4.431,11 TL/TON.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>AKTEM ELEKTRİK SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2605120356</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Kablo Teklifi (Alıcı: HB Elektrik Proje ve Müşavirlik San.Tic.Ltd.Şti., İlgili: Bayram Bey)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>1193813.54</v>
+      </c>
+      <c r="H108" t="n">
+        <v>7</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Alt Toplam 994.844,62 TL + KDV Toplamı 198.968,92 TL = Genel Toplam 1.193.813,54 TL. Toplam Kg: 1.879,50. Vade 90 gün, teslimat kendi çeki/sevk öncesi.</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J83"/>
+  <autoFilter ref="A1:J108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3923,7 +5019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1112"/>
+  <dimension ref="A1:L1269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -61524,8 +62620,8170 @@
         </is>
       </c>
     </row>
+    <row r="1113">
+      <c r="A1113" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1113" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Aktif yakalama ucu ortalama uyarım yolu DL=60mt (TESLA tipi paratoner ucu)</t>
+        </is>
+      </c>
+      <c r="G1113" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1113" s="3" t="n">
+        <v>4250</v>
+      </c>
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1113" s="3" t="n">
+        <v>8500</v>
+      </c>
+      <c r="L1113" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1114" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Yıldırım sayıcı (dijital)</t>
+        </is>
+      </c>
+      <c r="G1114" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1114" s="3" t="n">
+        <v>1750</v>
+      </c>
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1114" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L1114" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1115" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>Aktif paratoner test cihazı</t>
+        </is>
+      </c>
+      <c r="G1115" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1115" s="3" t="n">
+        <v>1750</v>
+      </c>
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1115" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L1115" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1116" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>50 mm2 elektrolitik bakır iletken</t>
+        </is>
+      </c>
+      <c r="G1116" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1116" s="3" t="n">
+        <v>325</v>
+      </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1116" s="3" t="n">
+        <v>42250</v>
+      </c>
+      <c r="L1116" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1117" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>Toprak elektrodu (çubuk) elektrolitik bakır, Ölçü: 1,5m</t>
+        </is>
+      </c>
+      <c r="G1117" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1117" s="3" t="n">
+        <v>3250</v>
+      </c>
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1117" s="3" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L1117" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1118" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>İletken koruyucu borusu</t>
+        </is>
+      </c>
+      <c r="G1118" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1118" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1118" s="3" t="n">
+        <v>5700</v>
+      </c>
+      <c r="L1118" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1119" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>19 mt. Galvanizli çelik poligon direk</t>
+        </is>
+      </c>
+      <c r="G1119" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1119" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1119" s="3" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L1119" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="n">
+        <v>1119</v>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1120" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Tespit kelepçesi (galvaniz çelik)</t>
+        </is>
+      </c>
+      <c r="G1120" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1120" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1120" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L1120" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="n">
+        <v>1120</v>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1121" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>Test klemensi</t>
+        </is>
+      </c>
+      <c r="G1121" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1121" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1121" s="3" t="n">
+        <v>5700</v>
+      </c>
+      <c r="L1121" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="n">
+        <v>1121</v>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1122" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Topraklama menholu (50x50x50cm)</t>
+        </is>
+      </c>
+      <c r="G1122" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1122" s="3" t="n">
+        <v>1750</v>
+      </c>
+      <c r="J1122" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1122" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L1122" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="n">
+        <v>1122</v>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>S NOVAGROUP MÜHENDİSLİK (YILKOMER)</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>20251209-2</t>
+        </is>
+      </c>
+      <c r="D1123" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>Yıldırımdan Korunma ve Topraklama Sistemi Ürün Teklifi</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Bakır eşpotansiyel bara (40x5x30mm)</t>
+        </is>
+      </c>
+      <c r="G1123" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1123" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J1123" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1123" s="3" t="n">
+        <v>1700</v>
+      </c>
+      <c r="L1123" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="n">
+        <v>1123</v>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1124" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Ø200 mm SN8 testsiz delikli muflu koruge boru (AYSAN)</t>
+        </is>
+      </c>
+      <c r="G1124" s="4" t="n">
+        <v>640</v>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>Metre</t>
+        </is>
+      </c>
+      <c r="I1124" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="J1124" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1124" s="3" t="n">
+        <v>89600</v>
+      </c>
+      <c r="L1124" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="n">
+        <v>1124</v>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1125" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>Ø200 mm SN8 testsiz muflu koruge boru (AYSAN)</t>
+        </is>
+      </c>
+      <c r="G1125" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>Metre</t>
+        </is>
+      </c>
+      <c r="I1125" s="3" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="J1125" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1125" s="3" t="n">
+        <v>13776</v>
+      </c>
+      <c r="L1125" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1126" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Ø300 mm SN8 testsiz delikli muflu koruge boru (AYSAN)</t>
+        </is>
+      </c>
+      <c r="G1126" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>Metre</t>
+        </is>
+      </c>
+      <c r="I1126" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="J1126" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1126" s="3" t="n">
+        <v>10360</v>
+      </c>
+      <c r="L1126" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="n">
+        <v>1126</v>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1127" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Ø200 mm koruge eşit te (AYSAN)</t>
+        </is>
+      </c>
+      <c r="G1127" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1127" s="3" t="n">
+        <v>403</v>
+      </c>
+      <c r="J1127" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1127" s="3" t="n">
+        <v>4433</v>
+      </c>
+      <c r="L1127" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1128" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>Ø200/45° koruge dirsek (AYSAN)</t>
+        </is>
+      </c>
+      <c r="G1128" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1128" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="J1128" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1128" s="3" t="n">
+        <v>5550</v>
+      </c>
+      <c r="L1128" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="n">
+        <v>1128</v>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1129" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Ø200/90° koruge dirsek (AYSAN)</t>
+        </is>
+      </c>
+      <c r="G1129" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1129" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="J1129" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1129" s="3" t="n">
+        <v>5060</v>
+      </c>
+      <c r="L1129" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="n">
+        <v>1129</v>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1130" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Ø50 mm koruge boru 450N</t>
+        </is>
+      </c>
+      <c r="G1130" s="4" t="n">
+        <v>660</v>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>Metre</t>
+        </is>
+      </c>
+      <c r="I1130" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J1130" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1130" s="3" t="n">
+        <v>12870</v>
+      </c>
+      <c r="L1130" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="n">
+        <v>1130</v>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1131" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>Ø75 mm koruge boru 450N</t>
+        </is>
+      </c>
+      <c r="G1131" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>Metre</t>
+        </is>
+      </c>
+      <c r="I1131" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J1131" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1131" s="3" t="n">
+        <v>19250</v>
+      </c>
+      <c r="L1131" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="n">
+        <v>1131</v>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>Ø100 mm SN8 testsiz muflu koruge boru (AYSAN)</t>
+        </is>
+      </c>
+      <c r="G1132" s="4" t="n">
+        <v>920</v>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1132" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="J1132" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1132" s="3" t="n">
+        <v>38640</v>
+      </c>
+      <c r="L1132" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="n">
+        <v>1132</v>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>BERKAN ELEKTRİK SANAYİ ve TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>12052026-1</t>
+        </is>
+      </c>
+      <c r="D1133" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Şırnak MIG - Koruge Boru Talebi</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Ø150 mm SN8 testsiz muflu koruge boru (AYSAN)</t>
+        </is>
+      </c>
+      <c r="G1133" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1133" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="J1133" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1133" s="3" t="n">
+        <v>5712</v>
+      </c>
+      <c r="L1133" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="n">
+        <v>1133</v>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>CONSOLE OTOMASYON</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>T21-0825-PGO1_Rev0</t>
+        </is>
+      </c>
+      <c r="D1134" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu PLC Teklifi</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>ControlEdge PLC Sistemi (1x CPU, 5x Universal IOM 16ch AI/AO/DI/DO 80 nokta, I/O Rack 8 Slot Red.Power, PS-DC 900ControlEdge58W, Profinet-Modbus lisansı, Experion HS SCADA, Windows 10 Enterprise LTSC, Dell iş istasyonu, mühendislik/programlama/test)</t>
+        </is>
+      </c>
+      <c r="G1134" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="I1134" s="3" t="n">
+        <v>45600</v>
+      </c>
+      <c r="J1134" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1134" s="3" t="n">
+        <v>45600</v>
+      </c>
+      <c r="L1134" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="n">
+        <v>1134</v>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>CONSOLE OTOMASYON</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>T21-0825-PGO1_Rev0</t>
+        </is>
+      </c>
+      <c r="D1135" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu PLC Teklifi</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Devreye alma hizmeti</t>
+        </is>
+      </c>
+      <c r="G1135" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>Hizmet</t>
+        </is>
+      </c>
+      <c r="I1135" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J1135" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1135" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L1135" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="n">
+        <v>1135</v>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1136" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>CORTEM EVL-080120 Ex LED yüksek tavan armatürü, 120W 13924 lm, Ex II 2G-Ex db eb op is IIC, Zone-1/21/22</t>
+        </is>
+      </c>
+      <c r="G1136" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1136" s="3" t="n">
+        <v>698</v>
+      </c>
+      <c r="J1136" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1136" s="3" t="n">
+        <v>2094</v>
+      </c>
+      <c r="L1136" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="n">
+        <v>1136</v>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1137" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>CORTEM GROUP CSC-216 Ex anahtar kutusu, 16A anahtar, Ex II 2G Ex d IIC Zone-1</t>
+        </is>
+      </c>
+      <c r="G1137" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1137" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="J1137" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1137" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="L1137" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="n">
+        <v>1137</v>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1138" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>CORTEM GROUP SX-26.1 Ex II 2GD Ex d IIC round junction box Ø89mm</t>
+        </is>
+      </c>
+      <c r="G1138" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1138" s="3" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="J1138" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1138" s="3" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="L1138" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="n">
+        <v>1138</v>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1139" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>BIMED KBA5MBNC M50x1,5 Ex-db/eb çelik zırhlı kablo glandi</t>
+        </is>
+      </c>
+      <c r="G1139" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1139" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="J1139" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1139" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="L1139" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="n">
+        <v>1139</v>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1140" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>BIMED M50 Metal Locknut</t>
+        </is>
+      </c>
+      <c r="G1140" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1140" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J1140" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1140" s="3" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="L1140" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="n">
+        <v>1140</v>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1141" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>BIMED M50 earth tag</t>
+        </is>
+      </c>
+      <c r="G1141" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1141" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J1141" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1141" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L1141" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="n">
+        <v>1141</v>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1142" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>BIMED M50 pvc shroud</t>
+        </is>
+      </c>
+      <c r="G1142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1142" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J1142" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1142" s="3" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="L1142" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="n">
+        <v>1142</v>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1143" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>BIMED KBA2LMBNC M25x1,5 Ex-db/eb çelik zırhlı kablo glandi</t>
+        </is>
+      </c>
+      <c r="G1143" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1143" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J1143" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1143" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="L1143" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="n">
+        <v>1143</v>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1144" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>BIMED M25 Metal Locknut</t>
+        </is>
+      </c>
+      <c r="G1144" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1144" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J1144" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1144" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L1144" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="n">
+        <v>1144</v>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1145" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>BIMED M25 earth tag</t>
+        </is>
+      </c>
+      <c r="G1145" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1145" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J1145" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1145" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L1145" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="n">
+        <v>1145</v>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1146" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>BIMED M25 pvc shroud</t>
+        </is>
+      </c>
+      <c r="G1146" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1146" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J1146" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1146" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L1146" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="n">
+        <v>1146</v>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1147" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>BIMED KBA1LMBNC M20x1,5 Ex-db/eb çelik zırhlı kablo glandi</t>
+        </is>
+      </c>
+      <c r="G1147" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1147" s="3" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="J1147" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1147" s="3" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="L1147" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1148" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>BIMED M20 Metal Locknut</t>
+        </is>
+      </c>
+      <c r="G1148" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1148" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J1148" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1148" s="3" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L1148" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="n">
+        <v>1148</v>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1149" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>BIMED M20 earth tag</t>
+        </is>
+      </c>
+      <c r="G1149" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1149" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J1149" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1149" s="3" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="L1149" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="n">
+        <v>1149</v>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>ELPİM Mühendislik Müşavirlik San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>2026/00000000399</t>
+        </is>
+      </c>
+      <c r="D1150" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Ex-proof Elektrik Malzemeleri Talebi (Firma: EXACONS)</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>BIMED M20 pvc shroud</t>
+        </is>
+      </c>
+      <c r="G1150" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1150" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J1150" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1150" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L1150" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1151" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>12" Pipe CS ASTM A106/API 5L GrB PSL1 BW ASME B36.10 SMLS PE SCH20 (DN300, 323,8x6,35)</t>
+        </is>
+      </c>
+      <c r="G1151" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1151" s="3" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="J1151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1151" s="3" t="n">
+        <v>1178.82</v>
+      </c>
+      <c r="L1151" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="n">
+        <v>1151</v>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1152" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>6" Pipe ASTM A106 GrB/A53 GrB SCH40 ASME B36.10 SAW-SAWL Beveled Ends (DN150, 168,3x7,11)</t>
+        </is>
+      </c>
+      <c r="G1152" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1152" s="3" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="J1152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1152" s="3" t="n">
+        <v>2116.92</v>
+      </c>
+      <c r="L1152" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="n">
+        <v>1152</v>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1153" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>6" Pipe CS ASTM A106/API 5L GrB PSL1 BW ASME B36.10 SMLS PE SCH20 (DN150, 168,3x7,11)</t>
+        </is>
+      </c>
+      <c r="G1153" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1153" s="3" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="J1153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1153" s="3" t="n">
+        <v>423.38</v>
+      </c>
+      <c r="L1153" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="n">
+        <v>1153</v>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1154" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>8" Pipe ASTM A106 GrB/API 5L GrB PSL1 SCH20 ASME 36.10 SAW-SAWL Beveled Ends (DN200, 219,1x6,35)</t>
+        </is>
+      </c>
+      <c r="G1154" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1154" s="3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="J1154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1154" s="3" t="n">
+        <v>8262.360000000001</v>
+      </c>
+      <c r="L1154" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="n">
+        <v>1154</v>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1155" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>8" Pipe ASTM A106 GrB/A53 GrB SCH40 ASME B36.10 SAW-SAWL Beveled Ends (DN200, 219,1x8,18)</t>
+        </is>
+      </c>
+      <c r="G1155" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1155" s="3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1155" s="3" t="n">
+        <v>1377.06</v>
+      </c>
+      <c r="L1155" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="n">
+        <v>1155</v>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1156" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>16" Pipe CS API 5L GrX60 COATED PSL2 WELDED BE SCHSTD ASME B36.10 (DN400, 406,4x9,53)</t>
+        </is>
+      </c>
+      <c r="G1156" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1156" s="3" t="n">
+        <v>362.61</v>
+      </c>
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1156" s="3" t="n">
+        <v>56567.78</v>
+      </c>
+      <c r="L1156" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="n">
+        <v>1156</v>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1157" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>8" Spiral Wound Gasket 304/Graphite-CS, Centering Ring 4.5mm, 150#, ASME B16.20 (DN200)</t>
+        </is>
+      </c>
+      <c r="G1157" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1157" s="3" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="J1157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1157" s="3" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="L1157" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="n">
+        <v>1157</v>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1158" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>8" Flange WN ASME B16.5 150# RF ASTM A105 (150 LB WN Flange, DN200)</t>
+        </is>
+      </c>
+      <c r="G1158" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1158" s="3" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="J1158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1158" s="3" t="n">
+        <v>885</v>
+      </c>
+      <c r="L1158" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="n">
+        <v>1158</v>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1159" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>16" 45 LR Elbow CS ASTM A234 WPB BW ASME B16.9 BE SCHSTD (DN400)</t>
+        </is>
+      </c>
+      <c r="G1159" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1159" s="3" t="n">
+        <v>216.33</v>
+      </c>
+      <c r="J1159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1159" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="L1159" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1160" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>6" 45 LR Elbow CS ASTM A234 WPB BW ASME B16.9 BE SCH40 (DN150)</t>
+        </is>
+      </c>
+      <c r="G1160" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1160" s="3" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="J1160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1160" s="3" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="L1160" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="n">
+        <v>1160</v>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1161" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>8" 45 LR Elbow CS ASTM A234 WPB BW ASME B16.9 BE SCH20 (DN200)</t>
+        </is>
+      </c>
+      <c r="G1161" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1161" s="3" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="J1161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1161" s="3" t="n">
+        <v>461.51</v>
+      </c>
+      <c r="L1161" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="n">
+        <v>1161</v>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1162" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>16" 90 LR Elbow CS ASTM A234 WPB BW ASME B16.9 BE SCHSTD (DN400)</t>
+        </is>
+      </c>
+      <c r="G1162" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1162" s="3" t="n">
+        <v>285.82</v>
+      </c>
+      <c r="J1162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1162" s="3" t="n">
+        <v>1143.29</v>
+      </c>
+      <c r="L1162" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1163" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>6" 90 LR Elbow CS ASTM A234 WPB BW ASME B16.9 BE SCH40 (DN150)</t>
+        </is>
+      </c>
+      <c r="G1163" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1163" s="3" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="J1163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1163" s="3" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="L1163" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1164" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>8" 90 LR Elbow CS ASTM A234 WPB BW ASME B16.9 BE SCH20 (DN200)</t>
+        </is>
+      </c>
+      <c r="G1164" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1164" s="3" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="J1164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1164" s="3" t="n">
+        <v>169.13</v>
+      </c>
+      <c r="L1164" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1165" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>M20 Hex Bolt Set, 25CrMo4, EN ISO 4014/4032/7089, EN10269</t>
+        </is>
+      </c>
+      <c r="G1165" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1165" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J1165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1165" s="3" t="n">
+        <v>119.57</v>
+      </c>
+      <c r="L1165" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="n">
+        <v>1165</v>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Hera Global Çelik Boru Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>FB1712-12089</t>
+        </is>
+      </c>
+      <c r="D1166" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Malzeme Listesi</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>M20 Stud Bolt with 2 Heavy Hex Nuts, ASTM A193 GrB7/A194 Gr2H, ASME B18.2.1/B18.2.2</t>
+        </is>
+      </c>
+      <c r="G1166" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>M/adet</t>
+        </is>
+      </c>
+      <c r="I1166" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J1166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1166" s="3" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="L1166" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="n">
+        <v>1166</v>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Arde Aydınlatma (Detay Aydınlatma)</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>7148</t>
+        </is>
+      </c>
+      <c r="D1167" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Yol Aydınlatma Armatürü Teklifi (Firma: HB Elektrik Proje ve Müşavirlik)</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>VANESSA ST (2x2) 75W 5700K 70CRI Asimetrik Lens 5050 LED Yol Aydınlatma (DTY.067.0055)</t>
+        </is>
+      </c>
+      <c r="G1167" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1167" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="J1167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1167" s="3" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L1167" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>ETE Enerji Tesisleri Endüstrisi Sanayi Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Ref yok (13.06.2026 teklifi)</t>
+        </is>
+      </c>
+      <c r="D1168" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Ex-Proof Elektrik Malzemeleri (Firma: Key Oil &amp; Gas, İlgili: Melih Serindere)</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Junction Box Type SB-282816, 280x280x160mm 1.5mm AISI316, Ex II 2G Ex eb IIC T6 Gb / Ex II 2D Ex tb IIIC T85 Db, IP66, ATEX/IECEx, marka TECHNOR ITALSMEA (JB TİP 1B, 6 çift)</t>
+        </is>
+      </c>
+      <c r="G1168" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1168" s="3" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="J1168" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1168" s="3" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="L1168" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="n">
+        <v>1168</v>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>ETE Enerji Tesisleri Endüstrisi Sanayi Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Ref yok (13.06.2026 teklifi)</t>
+        </is>
+      </c>
+      <c r="D1169" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Ex-Proof Elektrik Malzemeleri (Firma: Key Oil &amp; Gas, İlgili: Melih Serindere)</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Junction Box Type SB-383820, 380x380x200mm 1.5mm AISI316, Ex II 2G Ex eb IIC T6 Gb / Ex II 2D Ex tb IIIC T85 Db, IP66, ATEX/IECEx, marka TECHNOR ITALSMEA (JB TİP 2B, 12 çift)</t>
+        </is>
+      </c>
+      <c r="G1169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>Ad.</t>
+        </is>
+      </c>
+      <c r="I1169" s="3" t="n">
+        <v>602.5599999999999</v>
+      </c>
+      <c r="J1169" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1169" s="3" t="n">
+        <v>602.5599999999999</v>
+      </c>
+      <c r="L1169" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>VISVANA</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>T1-264106</t>
+        </is>
+      </c>
+      <c r="D1170" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Çamur Kutusu Teklifi (Şirket: KEYOİLGAS)</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Düz Tip Çamur Kutusu Class 150, 6", Maks 4 Bar, gövde çelik, filtre SS304 mesh 5mm, conta Viton, flanşlı, diferansiyel basınç göstergeli</t>
+        </is>
+      </c>
+      <c r="G1170" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1170" s="3" t="n">
+        <v>1380.93</v>
+      </c>
+      <c r="J1170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1170" s="3" t="n">
+        <v>4142.79</v>
+      </c>
+      <c r="L1170" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="n">
+        <v>1170</v>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>VISVANA</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>T1-264106</t>
+        </is>
+      </c>
+      <c r="D1171" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Çamur Kutusu Teklifi (Şirket: KEYOİLGAS)</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Düz Tip Çamur Kutusu Class 150, 6", Maks 4 Bar, gövde çelik, filtre SS304 mesh 5mm, conta EPDM, flanşlı, diferansiyel basınç göstergeli</t>
+        </is>
+      </c>
+      <c r="G1171" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1171" s="3" t="n">
+        <v>1200.81</v>
+      </c>
+      <c r="J1171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1171" s="3" t="n">
+        <v>2401.62</v>
+      </c>
+      <c r="L1171" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>EAE Elektrik Aydınlatma Endüstrisi San. ve Tic. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>11502376 Rev.0</t>
+        </is>
+      </c>
+      <c r="D1172" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>Şırnak Endüstriyel Tesis Aydınlatma Teklifi (Firma: Hb Elektrik Prj.Müş.San.Ve Tic.Ltd., Proje No: PA-0000040)</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>CN2 098D 40LN00 T2M-A 14K7 V6 (IP66, alüminyum enjeksiyon gövde, 98W, 14700 lm, 4000K, 80 CRI, direk montaj)</t>
+        </is>
+      </c>
+      <c r="G1172" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="I1172" s="3" t="n">
+        <v>159.61</v>
+      </c>
+      <c r="J1172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1172" s="3" t="n">
+        <v>2872.98</v>
+      </c>
+      <c r="L1172" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>EAE Elektrik Aydınlatma Endüstrisi San. ve Tic. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>11502376 Rev.0</t>
+        </is>
+      </c>
+      <c r="D1173" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Şırnak Endüstriyel Tesis Aydınlatma Teklifi (Firma: Hb Elektrik Prj.Müş.San.Ve Tic.Ltd., Proje No: PA-0000040)</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>YPL 041U 40OD00 4K3 125 NG 66 (IP66, plastik ekstrüzyon gövde, sıvaüstü, opal difüzör, 41W, 4300 lm, 4000K, 80CRI, 125cm)</t>
+        </is>
+      </c>
+      <c r="G1173" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="I1173" s="3" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="J1173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1173" s="3" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="L1173" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>EAE Elektrik Aydınlatma Endüstrisi San. ve Tic. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>11502376 Rev.0</t>
+        </is>
+      </c>
+      <c r="D1174" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Şırnak Endüstriyel Tesis Aydınlatma Teklifi (Firma: Hb Elektrik Prj.Müş.San.Ve Tic.Ltd., Proje No: PA-0000040)</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>HBC 107U 40EX00 110 12K1 Z1 (IP66, alüminyum enjeksiyon gövde, sıvaüstü, 107W, 12100 lm, 4000K, 80CRI, M20 rakor)</t>
+        </is>
+      </c>
+      <c r="G1174" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="I1174" s="3" t="n">
+        <v>1159.15</v>
+      </c>
+      <c r="J1174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1174" s="3" t="n">
+        <v>3477.45</v>
+      </c>
+      <c r="L1174" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>EAE Elektrik Aydınlatma Endüstrisi San. ve Tic. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>11502376 Rev.0</t>
+        </is>
+      </c>
+      <c r="D1175" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Şırnak Endüstriyel Tesis Aydınlatma Teklifi (Firma: Hb Elektrik Prj.Müş.San.Ve Tic.Ltd., Proje No: PA-0000040)</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>HBC EX Z1 kablo tavası ve tavan askı takımı</t>
+        </is>
+      </c>
+      <c r="G1175" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="I1175" s="3" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J1175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1175" s="3" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="L1175" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1176" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>Generatör Topraklaması Ölçüm ve Kontrol Rogarı (GTE-300-5, 50x50x50cm beton rogar)</t>
+        </is>
+      </c>
+      <c r="G1176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1176" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J1176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1176" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1176" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="n">
+        <v>1176</v>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1177" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Statik Elektrik Alıcı Levha (GTE-303)</t>
+        </is>
+      </c>
+      <c r="G1177" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1177" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J1177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1177" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="L1177" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1178" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Bakır Eşpotansiyel Bara 40x5x30mm (GEB-202)</t>
+        </is>
+      </c>
+      <c r="G1178" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1178" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J1178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1178" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="L1178" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="n">
+        <v>1178</v>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1179" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Galvanizli Şerit 40x3mm/40x4mm (GTE-136 D/MT)</t>
+        </is>
+      </c>
+      <c r="G1179" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1179" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J1179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1179" s="3" t="n">
+        <v>756</v>
+      </c>
+      <c r="L1179" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="n">
+        <v>1179</v>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1180" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Cadweld Kaynaklı Ek Noktası, 90gr kaynak tozuna kadar (150G20)</t>
+        </is>
+      </c>
+      <c r="G1180" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1180" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J1180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1180" s="3" t="n">
+        <v>975</v>
+      </c>
+      <c r="L1180" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="n">
+        <v>1180</v>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1181" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Termokaynak ürünü (GTE-401)</t>
+        </is>
+      </c>
+      <c r="G1181" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1181" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1181" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="L1181" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="n">
+        <v>1181</v>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1182" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Termokaynak ürünü (GTE-402)</t>
+        </is>
+      </c>
+      <c r="G1182" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1182" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1182" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1182" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1183" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Termokaynak ürünü (GTE-403)</t>
+        </is>
+      </c>
+      <c r="G1183" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1183" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J1183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1183" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1183" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="n">
+        <v>1183</v>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1184" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Termokaynak ürünü (GTE-404)</t>
+        </is>
+      </c>
+      <c r="G1184" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1184" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1184" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1184" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="n">
+        <v>1184</v>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1185" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Termokaynak ürünü (GTE-405)</t>
+        </is>
+      </c>
+      <c r="G1185" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1185" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J1185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1185" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="L1185" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="n">
+        <v>1185</v>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1186" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Elektrolitik Bakır Topraklama Çubuğu L=3mt Ø20mm (2xGTE-106-F+GTE-B+GTE-Ç+GTE-S)</t>
+        </is>
+      </c>
+      <c r="G1186" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1186" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="J1186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1186" s="3" t="n">
+        <v>4806</v>
+      </c>
+      <c r="L1186" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="n">
+        <v>1186</v>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1187" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>1x50mm² Çıplak Örgülü Bakır (50mm2/MT)</t>
+        </is>
+      </c>
+      <c r="G1187" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1187" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J1187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1187" s="3" t="n">
+        <v>810</v>
+      </c>
+      <c r="L1187" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="n">
+        <v>1187</v>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1188" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>1x95mm² Çıplak Örgülü Bakır (95mm2/MT)</t>
+        </is>
+      </c>
+      <c r="G1188" s="4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1188" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J1188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1188" s="3" t="n">
+        <v>24800</v>
+      </c>
+      <c r="L1188" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="n">
+        <v>1188</v>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1189" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Aktif Yakalama Ucu Ortalama Uyarım Yolu DL=60mt (TESLA)</t>
+        </is>
+      </c>
+      <c r="G1189" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1189" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="J1189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1189" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="L1189" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="n">
+        <v>1189</v>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1190" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Yıldırım Sayıcı (SAYAÇ-DİJİTAL)</t>
+        </is>
+      </c>
+      <c r="G1190" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1190" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="J1190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1190" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="L1190" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="n">
+        <v>1190</v>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1191" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Aktif Paratoner Test Cihazı (TESLA TESTER)</t>
+        </is>
+      </c>
+      <c r="G1191" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1191" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J1191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1191" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="L1191" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="n">
+        <v>1191</v>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1192" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>50mm² Elektrolitik Bakır İletken (50mm2 MONO/MT)</t>
+        </is>
+      </c>
+      <c r="G1192" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="I1192" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J1192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1192" s="3" t="n">
+        <v>1053</v>
+      </c>
+      <c r="L1192" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="n">
+        <v>1192</v>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1193" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Toprak Elektrodu (çubuk) Elektrolitik Bakır 1,5m (GTE-106-E+GTE-Ç+GTE-S+GTE-124-A EKO)</t>
+        </is>
+      </c>
+      <c r="G1193" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1193" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="J1193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1193" s="3" t="n">
+        <v>462</v>
+      </c>
+      <c r="L1193" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="n">
+        <v>1193</v>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1194" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>İletken Koruyucu Borusu (GB-420 D)</t>
+        </is>
+      </c>
+      <c r="G1194" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1194" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J1194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1194" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="L1194" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="n">
+        <v>1194</v>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1195" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Tespit Kelepçesi galvaniz çelik (BK-420 D)</t>
+        </is>
+      </c>
+      <c r="G1195" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1195" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J1195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1195" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L1195" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="n">
+        <v>1195</v>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1196" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Test Klemensi (GF-201 EKO)</t>
+        </is>
+      </c>
+      <c r="G1196" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1196" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1196" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="L1196" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="n">
+        <v>1196</v>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1197" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Topraklama Menholu 50x50x50cm (GTE-300-5)</t>
+        </is>
+      </c>
+      <c r="G1197" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1197" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J1197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1197" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="L1197" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="n">
+        <v>1197</v>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Bilinmeyen/olası S NOVAGROUP (YILKOMER) - USD Teklifi</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Ref yok (08.05.2026, TOPRAKLAMA+YILDIRIM SİSTEMİ)</t>
+        </is>
+      </c>
+      <c r="D1198" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Topraklama Sistemi + Yıldırımdan Korunma Sistemi (kombine BOM, USD)</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Bakır Eşpotansiyel Bara 40x5x30mm (GEB-202)</t>
+        </is>
+      </c>
+      <c r="G1198" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="I1198" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J1198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1198" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="L1198" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="n">
+        <v>1198</v>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Yaman Endüstriyel Otomasyon (Bülent Gürkanlı)</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>2026-06-09-001-KEY-R00</t>
+        </is>
+      </c>
+      <c r="D1199" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>TPAO Mehmet İrfan Güler Petrol Üretim İstasyonu Detay Mühendislik İşi - PLC Teklifi</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>PLC Sistemi: Pano (800x800x2000mm), ControlEdge PLC CPU, I/O modülleri, operatör istasyonları (2x Dell iş istasyonu 32GB+1TB SSD, 27" monitör), ağ ekipmanları, Windows 10/Experion HS SCADA/ControlEdge lisansları, mühendislik ve dokümantasyon</t>
+        </is>
+      </c>
+      <c r="G1199" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="I1199" s="3" t="n">
+        <v>57500</v>
+      </c>
+      <c r="J1199" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1199" s="3" t="n">
+        <v>57500</v>
+      </c>
+      <c r="L1199" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="n">
+        <v>1199</v>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Yaman Endüstriyel Otomasyon (Bülent Gürkanlı)</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>2026-06-09-001-KEY-R00</t>
+        </is>
+      </c>
+      <c r="D1200" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>TPAO Mehmet İrfan Güler Petrol Üretim İstasyonu Detay Mühendislik İşi - PLC Teklifi</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Devreye Alma Süpervizyonu (1 mühendis, 5 takvim günü, günde maks 10 saat saha çalışması)</t>
+        </is>
+      </c>
+      <c r="G1200" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>Hizmet</t>
+        </is>
+      </c>
+      <c r="I1200" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J1200" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1200" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L1200" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Burçelik Vana San. ve Tic. A.Ş. (Burcelik Valve)</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>AE26210 R0</t>
+        </is>
+      </c>
+      <c r="D1201" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu Detay Mühendislik İşi - Vana Paketi</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Vana paketi - ATTACHMENT-1 kapsamı (detaylı kalem dökümü bu proforma metninde yok, sadece toplam gösterilmiştir)</t>
+        </is>
+      </c>
+      <c r="G1201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>Paket</t>
+        </is>
+      </c>
+      <c r="I1201" s="3" t="n">
+        <v>239697.3</v>
+      </c>
+      <c r="J1201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1201" s="3" t="n">
+        <v>239697.3</v>
+      </c>
+      <c r="L1201" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>ELSU BORU ELEKTRİK PLASTİK İNŞ. TAAH. PAZ. NAK. SAN. TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>T2605-00705</t>
+        </is>
+      </c>
+      <c r="D1202" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Şırnak TPAO Mehmet İrfan Güler - 6 Inch Pompaj Hattı Yapım İşi (Koruge Boru)</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Ø25 mm Sıva Altı Elektrik Tesisatı Kangal Boru Siyah, Orta Seri 750N (152.1.1.01.00090)</t>
+        </is>
+      </c>
+      <c r="G1202" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1202" s="3" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="J1202" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1202" s="3" t="n">
+        <v>1510</v>
+      </c>
+      <c r="L1202" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>ELSU BORU ELEKTRİK PLASTİK İNŞ. TAAH. PAZ. NAK. SAN. TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>T2605-00705</t>
+        </is>
+      </c>
+      <c r="D1203" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Şırnak TPAO Mehmet İrfan Güler - 6 Inch Pompaj Hattı Yapım İşi (Koruge Boru)</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Ø50 mm Topraktaltı Elektrik Tesisatı Koruge Boru Siyah, Orta Seri 450N (153.6.3.01.00012)</t>
+        </is>
+      </c>
+      <c r="G1203" s="4" t="n">
+        <v>660</v>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1203" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J1203" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1203" s="3" t="n">
+        <v>10890</v>
+      </c>
+      <c r="L1203" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>ELSU BORU ELEKTRİK PLASTİK İNŞ. TAAH. PAZ. NAK. SAN. TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>T2605-00705</t>
+        </is>
+      </c>
+      <c r="D1204" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Şırnak TPAO Mehmet İrfan Güler - 6 Inch Pompaj Hattı Yapım İşi (Koruge Boru)</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Ø75 mm Topraktaltı Elektrik Tesisatı Koruge Boru Siyah, Orta Seri 450N (153.6.3.01.00019)</t>
+        </is>
+      </c>
+      <c r="G1204" s="4" t="n">
+        <v>702</v>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1204" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="J1204" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1204" s="3" t="n">
+        <v>18603</v>
+      </c>
+      <c r="L1204" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>ELSU BORU ELEKTRİK PLASTİK İNŞ. TAAH. PAZ. NAK. SAN. TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>T2605-00705</t>
+        </is>
+      </c>
+      <c r="D1205" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Şırnak TPAO Mehmet İrfan Güler - 6 Inch Pompaj Hattı Yapım İşi (Koruge Boru)</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Ø110 mm Topraktaltı Elektrik Tesisatı Koruge Boru Siyah, Orta Seri 450N (153.6.3.01.00009)</t>
+        </is>
+      </c>
+      <c r="G1205" s="4" t="n">
+        <v>924</v>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1205" s="3" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="J1205" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1205" s="3" t="n">
+        <v>32802</v>
+      </c>
+      <c r="L1205" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>ELSU BORU ELEKTRİK PLASTİK İNŞ. TAAH. PAZ. NAK. SAN. TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>T2605-00705</t>
+        </is>
+      </c>
+      <c r="D1206" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Şırnak TPAO Mehmet İrfan Güler - 6 Inch Pompaj Hattı Yapım İşi (Koruge Boru)</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Ø150 mm Topraktaltı Elektrik Tesisatı Koruge Boru Siyah, SN4 (153.6.3.01.00015)</t>
+        </is>
+      </c>
+      <c r="G1206" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="I1206" s="3" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="J1206" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1206" s="3" t="n">
+        <v>7862.4</v>
+      </c>
+      <c r="L1206" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Endress+Hauser Elektronik Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>2051095090 (Bütçesel Teklif)</t>
+        </is>
+      </c>
+      <c r="D1207" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Referans - Basınç/Sıcaklık/Seviye Enstrümantasyonu</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Deltabar PMD75B (PMD75B-67Q77/101) - Differential pressure transmitter, ATEX/IEC II 1/2G Ex ia IIC T6, 4-20mA HART, 3bar range</t>
+        </is>
+      </c>
+      <c r="G1207" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="I1207" s="3" t="n">
+        <v>2815.8</v>
+      </c>
+      <c r="J1207" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1207" s="3" t="n">
+        <v>5631.6</v>
+      </c>
+      <c r="L1207" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Endress+Hauser Elektronik Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>2051095090 (Bütçesel Teklif)</t>
+        </is>
+      </c>
+      <c r="D1208" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Referans - Basınç/Sıcaklık/Seviye Enstrümantasyonu</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Cerabar PMP71B (PMP71B-E3DR9/0) - Pressure transmitter, ATEX/IEC Ex ia/db IIC T6, 4-20mA HART, 100bar range</t>
+        </is>
+      </c>
+      <c r="G1208" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="I1208" s="3" t="n">
+        <v>1319.21</v>
+      </c>
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1208" s="3" t="n">
+        <v>2638.41</v>
+      </c>
+      <c r="L1208" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Endress+Hauser Elektronik Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>2051095090 (Bütçesel Teklif)</t>
+        </is>
+      </c>
+      <c r="D1209" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Referans - Basınç/Sıcaklık/Seviye Enstrümantasyonu</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>iTHERM ModuLine TM151 (TM151-243C6/101) - Modular thermometer, ATEX IECEx II1/2G Ex ia IIC T6, Pt100, -50...+400C</t>
+        </is>
+      </c>
+      <c r="G1209" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="I1209" s="3" t="n">
+        <v>780.8200000000001</v>
+      </c>
+      <c r="J1209" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1209" s="3" t="n">
+        <v>1561.64</v>
+      </c>
+      <c r="L1209" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Endress+Hauser Elektronik Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>2051095090 (Bütçesel Teklif)</t>
+        </is>
+      </c>
+      <c r="D1210" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Referans - Basınç/Sıcaklık/Seviye Enstrümantasyonu</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Micropilot FMR62B (FMR62B-2X061/101) - Radar level, 80GHz, ATEX/IEC Ex db IIC T6, 4-20mA HART, NPS4" Cl.150 flange</t>
+        </is>
+      </c>
+      <c r="G1210" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="I1210" s="3" t="n">
+        <v>4222.07</v>
+      </c>
+      <c r="J1210" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1210" s="3" t="n">
+        <v>8444.129999999999</v>
+      </c>
+      <c r="L1210" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Endress+Hauser Elektronik Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>2051095090 (Bütçesel Teklif)</t>
+        </is>
+      </c>
+      <c r="D1211" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>1-KEY-199 Referans - Basınç/Sıcaklık/Seviye Enstrümantasyonu</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Device Commissioning (XD22AB-18RR1/0) - 10 cihaz için devreye alma hizmeti</t>
+        </is>
+      </c>
+      <c r="G1211" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="I1211" s="3" t="n">
+        <v>2100.1</v>
+      </c>
+      <c r="J1211" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1211" s="3" t="n">
+        <v>2100.1</v>
+      </c>
+      <c r="L1211" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Bilinmeyen (Ref. Kod: FA26060801)</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>FA26060801</t>
+        </is>
+      </c>
+      <c r="D1212" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak Projesi - Yangın Hidrant Sistemi Malzemeleri</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Hidrant 100x65x65, 350 PSI</t>
+        </is>
+      </c>
+      <c r="G1212" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="I1212" s="3" t="n">
+        <v>863.37</v>
+      </c>
+      <c r="J1212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1212" s="3" t="n">
+        <v>11223.84</v>
+      </c>
+      <c r="L1212" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Bilinmeyen (Ref. Kod: FA26060801)</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>FA26060801</t>
+        </is>
+      </c>
+      <c r="D1213" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak Projesi - Yangın Hidrant Sistemi Malzemeleri</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Hidrant Dolabı 2½", Kumandalı Lans, Alüminyum Pres Döküm, 2½" 30m Yangın Hortumu İki Ucu Rekorlu</t>
+        </is>
+      </c>
+      <c r="G1213" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="I1213" s="3" t="n">
+        <v>729</v>
+      </c>
+      <c r="J1213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1213" s="3" t="n">
+        <v>9477</v>
+      </c>
+      <c r="L1213" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Bilinmeyen (Ref. Kod: FA26060801)</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>FA26060801</t>
+        </is>
+      </c>
+      <c r="D1214" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak Projesi - Yangın Hidrant Sistemi Malzemeleri</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>NRS Vana Post İndikatörlü, 6''</t>
+        </is>
+      </c>
+      <c r="G1214" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="I1214" s="3" t="n">
+        <v>2143.77</v>
+      </c>
+      <c r="J1214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1214" s="3" t="n">
+        <v>8575.07</v>
+      </c>
+      <c r="L1214" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>SCHNEIDER ELEKTRİK SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>PRF11052026.2</t>
+        </is>
+      </c>
+      <c r="D1215" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>Proforma Fatura (Bütçelendirme Teklifi) - Şırnak Endüstriyel Tesis (Müşteri: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>ADP Panosu (2100x3500x600mm), Prisma SET Form 4b &amp; 54</t>
+        </is>
+      </c>
+      <c r="G1215" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1215" s="3" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J1215" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1215" s="3" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L1215" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>SCHNEIDER ELEKTRİK SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>PRF11052026.2</t>
+        </is>
+      </c>
+      <c r="D1216" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Proforma Fatura (Bütçelendirme Teklifi) - Şırnak Endüstriyel Tesis (Müşteri: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Kompanzasyon Panosu (2100x1200x600mm), Prisma SET Form 2b &amp; 54</t>
+        </is>
+      </c>
+      <c r="G1216" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1216" s="3" t="n">
+        <v>9500</v>
+      </c>
+      <c r="J1216" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1216" s="3" t="n">
+        <v>9500</v>
+      </c>
+      <c r="L1216" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>ARLIGHT AYDINLATMA A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Proje Kodu 2026011437 / Referans SO26735</t>
+        </is>
+      </c>
+      <c r="D1217" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>Şırnak Endüstriyel Tesis Projesi Aydınlatma Teklifi (Müşteri: Hb Elektrik Proje ve Müşavirlik)</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>B0550STA 105W STARK LEDLİ Çevre ve Yol Armatürü, CRI:70, KLV:4000, MC:Ø60, PWR:105 (LKS111.1.1.FF.00 / 272281156)</t>
+        </is>
+      </c>
+      <c r="G1217" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1217" s="3" t="n">
+        <v>199.87</v>
+      </c>
+      <c r="J1217" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1217" s="3" t="n">
+        <v>3597.63</v>
+      </c>
+      <c r="L1217" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>ARLIGHT AYDINLATMA A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Proje Kodu 2026011437 / Referans SO26735</t>
+        </is>
+      </c>
+      <c r="D1218" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>Şırnak Endüstriyel Tesis Projesi Aydınlatma Teklifi (Müşteri: Hb Elektrik Proje ve Müşavirlik)</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>E1200LUM LEDLİ Plastik Etanj Sıva Üstü Armatür, CRI:80, KLV:4000, PWR:034 (LGS508.1.1.FF.00 / 4349703)</t>
+        </is>
+      </c>
+      <c r="G1218" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1218" s="3" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="J1218" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1218" s="3" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="L1218" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>MANFRED GELDBACH</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>ST26-003951 Rev.1</t>
+        </is>
+      </c>
+      <c r="D1219" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Bağlantı Elemanları</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>WN B16.5 150LB 8" RF STD/40 SA/A105N/C21 (161 0150219 S21BS)</t>
+        </is>
+      </c>
+      <c r="G1219" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1219" s="3" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="J1219" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1219" s="3" t="n">
+        <v>624.6</v>
+      </c>
+      <c r="L1219" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>MANFRED GELDBACH</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>ST26-003951 Rev.1</t>
+        </is>
+      </c>
+      <c r="D1220" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Bağlantı Elemanları</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>ELBOW 45° LR 16" STD 9,53mm B16.9 WPB SMLS (105 0406045 S70BB)</t>
+        </is>
+      </c>
+      <c r="G1220" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1220" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="J1220" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1220" s="3" t="n">
+        <v>729</v>
+      </c>
+      <c r="L1220" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>MANFRED GELDBACH</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>ST26-003951 Rev.1</t>
+        </is>
+      </c>
+      <c r="D1221" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Bağlantı Elemanları</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>ELBOW 45° LR 6" STD/40 7,11mm B16.9 WPB SMLS (105 0168045 S70BB)</t>
+        </is>
+      </c>
+      <c r="G1221" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1221" s="3" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="J1221" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1221" s="3" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="L1221" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>MANFRED GELDBACH</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>ST26-003951 Rev.1</t>
+        </is>
+      </c>
+      <c r="D1222" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Bağlantı Elemanları</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>ELBOW 45° LR 8" SCH20 6,35mm B16.9 WPB SMLS (105 0219045 S7022)</t>
+        </is>
+      </c>
+      <c r="G1222" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1222" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="J1222" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1222" s="3" t="n">
+        <v>506</v>
+      </c>
+      <c r="L1222" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>MANFRED GELDBACH</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>ST26-003951 Rev.1</t>
+        </is>
+      </c>
+      <c r="D1223" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Bağlantı Elemanları</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>ELBOW 90° LR 16" STD 9,53mm B16.9 WPB SMLS (105 0406090 S70BB)</t>
+        </is>
+      </c>
+      <c r="G1223" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1223" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="J1223" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1223" s="3" t="n">
+        <v>972</v>
+      </c>
+      <c r="L1223" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>MANFRED GELDBACH</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>ST26-003951 Rev.1</t>
+        </is>
+      </c>
+      <c r="D1224" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Bağlantı Elemanları</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>ELBOW 90° LR 6" STD/40 7,11mm B16.9 WPB SMLS (105 0168090 S70BB)</t>
+        </is>
+      </c>
+      <c r="G1224" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1224" s="3" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="J1224" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1224" s="3" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="L1224" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>MANFRED GELDBACH</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>ST26-003951 Rev.1</t>
+        </is>
+      </c>
+      <c r="D1225" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Bağlantı Elemanları</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>ELBOW 90° LR 8" SCH20 6,35mm B16.9 WPB SMLS (105 0219090 S7022)</t>
+        </is>
+      </c>
+      <c r="G1225" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1225" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J1225" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1225" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="L1225" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>VALFTEK</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>26-0215</t>
+        </is>
+      </c>
+      <c r="D1226" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Küresel Vana Talebi (LF2/S355J2 gövde, RPTFE grafit sızdırmazlık, AISI316 küre/mil, üç parçalı tam geçişli dişli)</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>BONETTI dövme krb. çelik küresel vana 800lb 1/2" Tip:SFA</t>
+        </is>
+      </c>
+      <c r="G1226" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>ad.</t>
+        </is>
+      </c>
+      <c r="I1226" s="3" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J1226" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1226" s="3" t="n">
+        <v>190.2</v>
+      </c>
+      <c r="L1226" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="n">
+        <v>1226</v>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>VALFTEK</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>26-0215</t>
+        </is>
+      </c>
+      <c r="D1227" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>Küresel Vana Talebi (LF2/S355J2 gövde, RPTFE grafit sızdırmazlık, AISI316 küre/mil, üç parçalı tam geçişli dişli)</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>BONETTI dövme krb. çelik küresel vana 600lb 2" Tip:SFA</t>
+        </is>
+      </c>
+      <c r="G1227" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>ad.</t>
+        </is>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>240.8</v>
+      </c>
+      <c r="J1227" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1227" s="3" t="n">
+        <v>240.8</v>
+      </c>
+      <c r="L1227" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>VALFTEK</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>26-0215</t>
+        </is>
+      </c>
+      <c r="D1228" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>Küresel Vana Talebi (LF2/S355J2 gövde, RPTFE grafit sızdırmazlık, AISI316 küre/mil, üç parçalı tam geçişli dişli)</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>BONETTI dövme krb. çelik küresel vana 800lb 3/4" Tip:SFA</t>
+        </is>
+      </c>
+      <c r="G1228" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>ad.</t>
+        </is>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="J1228" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1228" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="L1228" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="n">
+        <v>1228</v>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>VALFTEK</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>26-0215</t>
+        </is>
+      </c>
+      <c r="D1229" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>Küresel Vana Talebi (LF2/S355J2 gövde, RPTFE grafit sızdırmazlık, AISI316 küre/mil, üç parçalı tam geçişli dişli)</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>BONETTI dövme krb. çelik küresel vana 800lb 1/2" Tip:SFA</t>
+        </is>
+      </c>
+      <c r="G1229" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>ad.</t>
+        </is>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J1229" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1229" s="3" t="n">
+        <v>190.2</v>
+      </c>
+      <c r="L1229" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="n">
+        <v>1229</v>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>VALFTEK</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>26-0215</t>
+        </is>
+      </c>
+      <c r="D1230" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>Küresel Vana Talebi (LF2/S355J2 gövde, RPTFE grafit sızdırmazlık, AISI316 küre/mil, üç parçalı tam geçişli dişli)</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>BONETTI dövme krb. çelik küresel vana 800lb 1/2" Tip:SFA</t>
+        </is>
+      </c>
+      <c r="G1230" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>ad.</t>
+        </is>
+      </c>
+      <c r="I1230" s="3" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J1230" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1230" s="3" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="L1230" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="n">
+        <v>1230</v>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>VALFTEK</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>26-0215</t>
+        </is>
+      </c>
+      <c r="D1231" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>Küresel Vana Talebi (LF2/S355J2 gövde, RPTFE grafit sızdırmazlık, AISI316 küre/mil, üç parçalı tam geçişli dişli)</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>BONETTI dövme krb. çelik küresel vana 800lb 3/4" Tip:SFA</t>
+        </is>
+      </c>
+      <c r="G1231" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>ad.</t>
+        </is>
+      </c>
+      <c r="I1231" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="J1231" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1231" s="3" t="n">
+        <v>462</v>
+      </c>
+      <c r="L1231" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="n">
+        <v>1231</v>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>VALFTEK</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>26-0215</t>
+        </is>
+      </c>
+      <c r="D1232" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>Küresel Vana Talebi (LF2/S355J2 gövde, RPTFE grafit sızdırmazlık, AISI316 küre/mil, üç parçalı tam geçişli dişli)</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>BONETTI dövme krb. çelik küresel vana 800lb 1/2" Tip:SFA</t>
+        </is>
+      </c>
+      <c r="G1232" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>ad.</t>
+        </is>
+      </c>
+      <c r="I1232" s="3" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J1232" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1232" s="3" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="L1232" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="n">
+        <v>1232</v>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>VALFTEK</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>26-0215</t>
+        </is>
+      </c>
+      <c r="D1233" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>Küresel Vana Talebi (LF2/S355J2 gövde, RPTFE grafit sızdırmazlık, AISI316 küre/mil, üç parçalı tam geçişli dişli)</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>BONETTI dövme krb. çelik küresel vana 800lb 3/4" Tip:SFA</t>
+        </is>
+      </c>
+      <c r="G1233" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>ad.</t>
+        </is>
+      </c>
+      <c r="I1233" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="J1233" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1233" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="L1233" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="n">
+        <v>1233</v>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>AKEL BORU SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>S101534</t>
+        </is>
+      </c>
+      <c r="D1234" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Talebi (Müşteri: KEY OİL GAS)</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>323,8 x 8,38 mm | ASTM A53 A106 API 5L GrB - PSL1, Gürcistan, vernikli, kaynak ağızlı, 6,0-6,1m boy</t>
+        </is>
+      </c>
+      <c r="G1234" s="4" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1234" s="3" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="J1234" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1234" s="3" t="n">
+        <v>1331.3</v>
+      </c>
+      <c r="L1234" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="n">
+        <v>1234</v>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>AKEL BORU SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>S101534</t>
+        </is>
+      </c>
+      <c r="D1235" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Talebi (Müşteri: KEY OİL GAS)</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>168,3 x 7,11 mm | ASTM A53 A106 API 5L GrB - PSL1, Gürcistan, vernikli, kaynak ağızlı, 6,0-6,1m boy</t>
+        </is>
+      </c>
+      <c r="G1235" s="4" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1235" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="J1235" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1235" s="3" t="n">
+        <v>1923.9</v>
+      </c>
+      <c r="L1235" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="n">
+        <v>1235</v>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>AKEL BORU SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>S101534</t>
+        </is>
+      </c>
+      <c r="D1236" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Talebi (Müşteri: KEY OİL GAS)</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>168,3 x 6,35 mm | ASTM A53 A106 API 5L GrB - PSL1, Gürcistan, vernikli, kaynak ağızlı, 6,0-6,1m boy</t>
+        </is>
+      </c>
+      <c r="G1236" s="4" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1236" s="3" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="J1236" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1236" s="3" t="n">
+        <v>345.46</v>
+      </c>
+      <c r="L1236" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="n">
+        <v>1236</v>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>AKEL BORU SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>S101534</t>
+        </is>
+      </c>
+      <c r="D1237" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Talebi (Müşteri: KEY OİL GAS)</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>219,1 x 6,35 mm | ASTM A53 A106 API 5L GrB - PSL1, Gürcistan, vernikli, kaynak ağızlı, 10,0-12,0m boy</t>
+        </is>
+      </c>
+      <c r="G1237" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1237" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J1237" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1237" s="3" t="n">
+        <v>6900</v>
+      </c>
+      <c r="L1237" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="n">
+        <v>1237</v>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>AKEL BORU SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>S101534</t>
+        </is>
+      </c>
+      <c r="D1238" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Talebi (Müşteri: KEY OİL GAS)</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>219,1 x 8,18 mm | ASTM A53 A106 API 5L GrB - PSL1, Gürcistan, korumasız, kaynak ağızlı, 6,0-6,1m boy</t>
+        </is>
+      </c>
+      <c r="G1238" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1238" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="J1238" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1238" s="3" t="n">
+        <v>1437</v>
+      </c>
+      <c r="L1238" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="n">
+        <v>1238</v>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>AKEL BORU SAN. VE TİC. A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>S101534</t>
+        </is>
+      </c>
+      <c r="D1239" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>TPAO Şırnak MIG - Boru Talebi (Müşteri: KEY OİL GAS)</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>406,4 x 9,53 mm | API 5L GrX60-PSL2, Avrupa, korumasız, düz, 10,0-12,0m boy</t>
+        </is>
+      </c>
+      <c r="G1239" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1239" s="3" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="J1239" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1239" s="3" t="n">
+        <v>52455</v>
+      </c>
+      <c r="L1239" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="n">
+        <v>1239</v>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1240" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Pvc Topraklama Test Rogarı (ET.PVC.TR.400)</t>
+        </is>
+      </c>
+      <c r="G1240" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1240" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J1240" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1240" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L1240" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="n">
+        <v>1240</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1241" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Statik Topraklama Levhası (ET.C.STL.25010)</t>
+        </is>
+      </c>
+      <c r="G1241" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1241" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1241" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="L1241" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="n">
+        <v>1241</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1242" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>40x5x300mm Eşpotansiyel Bara (ET.FEC.EPSİ.40530)</t>
+        </is>
+      </c>
+      <c r="G1242" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1242" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="J1242" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1242" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="L1242" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="n">
+        <v>1242</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1243" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Beton Topraklama Test Rogarı 600x600x600mm (ET.BTN.TR.600600)</t>
+        </is>
+      </c>
+      <c r="G1243" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1243" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J1243" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1243" s="3" t="n">
+        <v>2295</v>
+      </c>
+      <c r="L1243" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="n">
+        <v>1243</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1244" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>40x3 Galvaniz Topraklama Şeridi "Rulo" (ET.FD.TS.403)</t>
+        </is>
+      </c>
+      <c r="G1244" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1244" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J1244" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1244" s="3" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="L1244" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="n">
+        <v>1244</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1245" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>90 F 20 Termo Kaynak Tozu (ET.00.TKT.90)</t>
+        </is>
+      </c>
+      <c r="G1245" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1245" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1245" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1245" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="L1245" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="n">
+        <v>1245</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1246" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Termo Kaynak Potası "C Tipi" (ET.00.TKP.C.CE2.2025)</t>
+        </is>
+      </c>
+      <c r="G1246" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1246" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="J1246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1246" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="L1246" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="n">
+        <v>1246</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1247" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Pota Kazıyıcısı (ET.00.TPK)</t>
+        </is>
+      </c>
+      <c r="G1247" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1247" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J1247" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1247" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1247" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="n">
+        <v>1247</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1248" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Pota Pensesi L 160 (ET.00.TPP)</t>
+        </is>
+      </c>
+      <c r="G1248" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1248" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J1248" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1248" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="L1248" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="n">
+        <v>1248</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1249" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Pota Fırçası (ET.00.TPF)</t>
+        </is>
+      </c>
+      <c r="G1249" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1249" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J1249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1249" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1249" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="n">
+        <v>1249</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1250" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Ø20/3000mm Som Bakır Topraklama Elektrodu "Sivri Uç" (ET.C.TES.20300)</t>
+        </is>
+      </c>
+      <c r="G1250" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1250" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="J1250" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1250" s="3" t="n">
+        <v>3780</v>
+      </c>
+      <c r="L1250" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="n">
+        <v>1250</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1251" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>50mm² Örgülü Bakır Tel (ET.C.SW.50)</t>
+        </is>
+      </c>
+      <c r="G1251" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1251" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J1251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1251" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="L1251" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="n">
+        <v>1251</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1252" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>95mm² Örgülü Bakır Tel (ET.C.SW.95)</t>
+        </is>
+      </c>
+      <c r="G1252" s="4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1252" s="3" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="J1252" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1252" s="3" t="n">
+        <v>22528</v>
+      </c>
+      <c r="L1252" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="n">
+        <v>1252</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1253" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>1x50mm² NYA Kablo "Sarı-Yeşil" (ET.İCSY.SW.50)</t>
+        </is>
+      </c>
+      <c r="G1253" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1253" s="3" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="J1253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1253" s="3" t="n">
+        <v>1598.4</v>
+      </c>
+      <c r="L1253" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="n">
+        <v>1253</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1254" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>1x70mm² NYA Kablo "Sarı-Yeşil" (ET.İCSY.SW.70)</t>
+        </is>
+      </c>
+      <c r="G1254" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1254" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J1254" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1254" s="3" t="n">
+        <v>768</v>
+      </c>
+      <c r="L1254" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="n">
+        <v>1254</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>ESCO ELEKTRİK SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>2026001409 Rev-000001</t>
+        </is>
+      </c>
+      <c r="D1255" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Topraklama Malzemeleri Teklifi (Alıcı: HB Elektrik Proje ve Müş.Ltd.Şti.)</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>1x16mm² NYA Kablo "Sarı-Yeşil" (ET.İCSY.SW.16)</t>
+        </is>
+      </c>
+      <c r="G1255" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="I1255" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J1255" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1255" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="L1255" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="n">
+        <v>1255</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>DZA MÜHENDİSLİK - Ömer Ulukan Reşitoğlu</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>260622-024</t>
+        </is>
+      </c>
+      <c r="D1256" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Ham Petrol Üretim İstasyonu - Zemin Çivisi Yapım İşi</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Zemin Çivisi Yapım İşi</t>
+        </is>
+      </c>
+      <c r="G1256" s="4" t="n">
+        <v>264</v>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="I1256" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J1256" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1256" s="3" t="n">
+        <v>5280000</v>
+      </c>
+      <c r="L1256" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="n">
+        <v>1256</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>DZA MÜHENDİSLİK - Ömer Ulukan Reşitoğlu</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>260622-024</t>
+        </is>
+      </c>
+      <c r="D1257" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Ham Petrol Üretim İstasyonu - Zemin Çivisi Yapım İşi</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Makina Nakliye</t>
+        </is>
+      </c>
+      <c r="G1257" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="I1257" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J1257" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1257" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L1257" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="n">
+        <v>1257</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Hacı Ayvaz Endüstriyel Mamüller Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>STT0151405</t>
+        </is>
+      </c>
+      <c r="D1258" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Yangın Hidrantı ve Vana Teklifi</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>AYVAZ Yer Üstü Yangın Hidrantı GG25 DN100 (170cm), gövde GG-25 pik döküm, hareket mili X20Cr13, sürgü contası EPDM, PN16, TSE/CE belgeli</t>
+        </is>
+      </c>
+      <c r="G1258" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1258" s="3" t="n">
+        <v>24465</v>
+      </c>
+      <c r="J1258" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1258" s="3" t="n">
+        <v>24465</v>
+      </c>
+      <c r="L1258" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="n">
+        <v>1258</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Hacı Ayvaz Endüstriyel Mamüller Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>STT0151405</t>
+        </is>
+      </c>
+      <c r="D1259" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Yangın Hidrantı ve Vana Teklifi</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Hidrant Dirsek GGG50 DN100</t>
+        </is>
+      </c>
+      <c r="G1259" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1259" s="3" t="n">
+        <v>3892</v>
+      </c>
+      <c r="J1259" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1259" s="3" t="n">
+        <v>3892</v>
+      </c>
+      <c r="L1259" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="n">
+        <v>1259</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Hacı Ayvaz Endüstriyel Mamüller Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>STT0151405</t>
+        </is>
+      </c>
+      <c r="D1260" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Yangın Hidrantı ve Vana Teklifi</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>AYVAZ NRS Yükselmeyen Milli Sürgülü Vana (Gate Vana) PN16 DIN DN100, UL Listeli/FM Onaylı, 300PSI çalışma/600PSI test basıncı</t>
+        </is>
+      </c>
+      <c r="G1260" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1260" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="J1260" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1260" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="L1260" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="n">
+        <v>1260</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Hacı Ayvaz Endüstriyel Mamüller Sanayi ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>STT0151405</t>
+        </is>
+      </c>
+      <c r="D1261" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Yangın Hidrantı ve Vana Teklifi</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>AYVAZ Dikey İndikatör L:1270mm, gövde demir döküm, mil karbon çelik</t>
+        </is>
+      </c>
+      <c r="G1261" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1261" s="3" t="n">
+        <v>770</v>
+      </c>
+      <c r="J1261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1261" s="3" t="n">
+        <v>770</v>
+      </c>
+      <c r="L1261" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="n">
+        <v>1261</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Bilinmeyen (muhtemelen Klinger Turkey sevkiyatına ait iç taşıma maliyeti hesabı)</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Ref yok - Demir Profil ve Sac Taşıma Birim Fiyatı Tespiti</t>
+        </is>
+      </c>
+      <c r="D1262" s="2" t="n"/>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Ereğli OSB - Şırnak MIG Proje Şantiyesi Nakliye Bedeli Hesabı</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Demir Profil ve Sac Taşıma Bedeli: Ereğli OSB - Şırnak merkez 1500km + Şırnak merkez - şantiye 80km, zorluk katsayısı 1,35 (1250 rakım/dağlık arazi), %25 yüklenici karı dahil</t>
+        </is>
+      </c>
+      <c r="G1262" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>TON</t>
+        </is>
+      </c>
+      <c r="I1262" s="3" t="n">
+        <v>4431.11</v>
+      </c>
+      <c r="J1262" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1262" s="3" t="n">
+        <v>4431.11</v>
+      </c>
+      <c r="L1262" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="n">
+        <v>1262</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>AKTEM ELEKTRİK SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>2605120356</t>
+        </is>
+      </c>
+      <c r="D1263" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Kablo Teklifi (Alıcı: HB Elektrik Proje ve Müşavirlik San.Tic.Ltd.Şti., İlgili: Bayram Bey)</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Öznur YVV-R (NYY) 1x70 mm² 0,6/1 kV Eca Siyah Yekpare</t>
+        </is>
+      </c>
+      <c r="G1263" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I1263" s="3" t="n">
+        <v>479.71</v>
+      </c>
+      <c r="J1263" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1263" s="3" t="n">
+        <v>76753.60000000001</v>
+      </c>
+      <c r="L1263" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="n">
+        <v>1263</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>AKTEM ELEKTRİK SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>2605120356</t>
+        </is>
+      </c>
+      <c r="D1264" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Kablo Teklifi (Alıcı: HB Elektrik Proje ve Müşavirlik San.Tic.Ltd.Şti., İlgili: Bayram Bey)</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Öznur YVV-U (NYY) 5x2,5 mm² Mv-Kh-Syh-Gr-S/Y 0,6/1 kV Eca Siyah Yekpare</t>
+        </is>
+      </c>
+      <c r="G1264" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I1264" s="3" t="n">
+        <v>108.57</v>
+      </c>
+      <c r="J1264" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1264" s="3" t="n">
+        <v>54285</v>
+      </c>
+      <c r="L1264" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="n">
+        <v>1264</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>AKTEM ELEKTRİK SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>2605120356</t>
+        </is>
+      </c>
+      <c r="D1265" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Kablo Teklifi (Alıcı: HB Elektrik Proje ve Müşavirlik San.Tic.Ltd.Şti., İlgili: Bayram Bey)</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>Öznur YVV-U (NYY) 5x4 mm² Mv-Kh-Syh-Gr-S/Y 0,6/1 kV Eca Siyah Yekpare</t>
+        </is>
+      </c>
+      <c r="G1265" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I1265" s="3" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="J1265" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1265" s="3" t="n">
+        <v>42562.52</v>
+      </c>
+      <c r="L1265" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="n">
+        <v>1265</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>AKTEM ELEKTRİK SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>2605120356</t>
+        </is>
+      </c>
+      <c r="D1266" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Kablo Teklifi (Alıcı: HB Elektrik Proje ve Müşavirlik San.Tic.Ltd.Şti., İlgili: Bayram Bey)</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Öznur YVV-U (NYY) 5x6 mm² Mv-Kh-Syh-Gr-S/Y 0,6/1 kV Eca Siyah Yekpare</t>
+        </is>
+      </c>
+      <c r="G1266" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I1266" s="3" t="n">
+        <v>237.16</v>
+      </c>
+      <c r="J1266" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1266" s="3" t="n">
+        <v>26087.6</v>
+      </c>
+      <c r="L1266" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="n">
+        <v>1266</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>AKTEM ELEKTRİK SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>2605120356</t>
+        </is>
+      </c>
+      <c r="D1267" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Kablo Teklifi (Alıcı: HB Elektrik Proje ve Müşavirlik San.Tic.Ltd.Şti., İlgili: Bayram Bey)</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Öznur YVV-R (NYY) 5x16 mm² Mv-Kh-Syh-Gr-S/Y 0,6/1 kV Eca Siyah Yekpare</t>
+        </is>
+      </c>
+      <c r="G1267" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I1267" s="3" t="n">
+        <v>614.46</v>
+      </c>
+      <c r="J1267" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1267" s="3" t="n">
+        <v>49156.8</v>
+      </c>
+      <c r="L1267" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="n">
+        <v>1267</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>AKTEM ELEKTRİK SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>2605120356</t>
+        </is>
+      </c>
+      <c r="D1268" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Kablo Teklifi (Alıcı: HB Elektrik Proje ve Müşavirlik San.Tic.Ltd.Şti., İlgili: Bayram Bey)</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Öznur YVV-R (NYY) 3x50/25 mm² Mv-Kh-Syh-Gr 0,6/1 kV Eca Siyah Yekpare</t>
+        </is>
+      </c>
+      <c r="G1268" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I1268" s="3" t="n">
+        <v>1186.57</v>
+      </c>
+      <c r="J1268" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1268" s="3" t="n">
+        <v>272911.1</v>
+      </c>
+      <c r="L1268" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="n">
+        <v>1268</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>AKTEM ELEKTRİK SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>2605120356</t>
+        </is>
+      </c>
+      <c r="D1269" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Kablo Teklifi (Alıcı: HB Elektrik Proje ve Müşavirlik San.Tic.Ltd.Şti., İlgili: Bayram Bey)</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Öznur YVV-R (NYY) 3x120/70 mm² Mv-Kh-Syh-Gr 0,6/1 kV Eca Siyah Yekpare</t>
+        </is>
+      </c>
+      <c r="G1269" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I1269" s="3" t="n">
+        <v>2956.8</v>
+      </c>
+      <c r="J1269" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1269" s="3" t="n">
+        <v>473088</v>
+      </c>
+      <c r="L1269" t="inlineStr">
+        <is>
+          <t>199TPAO_397kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1112"/>
+  <autoFilter ref="A1:L1269"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/PROFORMA_FIYAT_LISTESI.xlsx
+++ b/PROFORMA_FIYAT_LISTESI.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Kalem Detay" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1288</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5007,8 +5007,184 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PROTAŞ PROJE MÜHENDİSLİK (marka: Prosense)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>VTK03214</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Exproof Ekipman Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>1769.45</v>
+      </c>
+      <c r="H109" t="n">
+        <v>6</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Alt Toplam 1.474,54 EUR + KDV 294,91 EUR = Genel Toplam 1.769,45 EUR</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SETA ÇELİK</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Teklif Konusu: Çelik Tank İmalatı (Rev.1)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu - Çelik Tank İmalatı (20.000/7.000/2.000 BBL)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>1005906.27</v>
+      </c>
+      <c r="H110" t="n">
+        <v>6</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>KDV hariç; ağırlıklar yaklaşık, nihai ağırlıklar projelendirme sonrası belli olacak</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PATRİON İLERİ TEKNOLOJİ SİSTEMLERİ A.Ş.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PK100375</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Şırnak ADP + Kompanzasyon Pano İmalatı (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>35385.1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Toplam 29.487,58 EUR + KDV %20 5.897,52 EUR = Genel Toplam 35.385,10 EUR</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>YAKAN AYDINLATMA (Selçuk Yakan)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>003472</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Kamera Direği Malzemeleri (Alıcı: HB Elektrik - Bayram Çolak)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>14875.2</v>
+      </c>
+      <c r="H112" t="n">
+        <v>5</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>İndirimli Toplam (Liste fiyatı üzerinden %45/%0 iskonto) 12.396,00 USD + KDV %20 2.479,20 USD = Toplam Tutar 14.875,20 USD. Not: Prosense/R.Stahl marka iki adet 'Terminal Box Ex e' teknik teklifi (Proposal 33328/33329 Rev.0) bu dosyada fiyatsız (sadece teknik spesifikasyon) olarak yer alıyor, listeye eklenmedi.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J108"/>
+  <autoFilter ref="A1:J112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5019,7 +5195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1269"/>
+  <dimension ref="A1:L1288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -70782,8 +70958,996 @@
         </is>
       </c>
     </row>
+    <row r="1270">
+      <c r="A1270" t="n">
+        <v>1269</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>PROTAŞ PROJE MÜHENDİSLİK (marka: Prosense)</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>VTK03214</t>
+        </is>
+      </c>
+      <c r="D1270" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Exproof Ekipman Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>EVFRL.236-NK Ex-proof LED Floresan Aydınlatma Armatürü, 2x45W, 11880 Lümen, Ex-d Zone1/21</t>
+        </is>
+      </c>
+      <c r="G1270" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1270" s="3" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="J1270" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1270" s="3" t="n">
+        <v>1108.8</v>
+      </c>
+      <c r="L1270" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="n">
+        <v>1270</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>PROTAŞ PROJE MÜHENDİSLİK (marka: Prosense)</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>VTK03214</t>
+        </is>
+      </c>
+      <c r="D1271" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Exproof Ekipman Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>EFSC.21 Ex-proof Monofaze Elektrik Anahtarı (0-1 Aç/Kapa), 1x20A, 3/4NPT, Zone1/21</t>
+        </is>
+      </c>
+      <c r="G1271" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1271" s="3" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="J1271" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1271" s="3" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="L1271" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>PROTAŞ PROJE MÜHENDİSLİK (marka: Prosense)</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>VTK03214</t>
+        </is>
+      </c>
+      <c r="D1272" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Exproof Ekipman Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>GUFT.26 Ayaklı Ex-proof Bağlantı Buatı, Üç Girişli, 133x133x82mm, IP6X, Ex-d, Zone1/21</t>
+        </is>
+      </c>
+      <c r="G1272" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1272" s="3" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="J1272" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1272" s="3" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="L1272" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>PROTAŞ PROJE MÜHENDİSLİK (marka: Prosense)</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>VTK03214</t>
+        </is>
+      </c>
+      <c r="D1273" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Exproof Ekipman Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>KBA-2M Ex-proof Zırhlı Kablo Rakoru, IP66, M25x1.5, Sıkma Aralığı 12-21mm</t>
+        </is>
+      </c>
+      <c r="G1273" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1273" s="3" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="J1273" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1273" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L1273" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>PROTAŞ PROJE MÜHENDİSLİK (marka: Prosense)</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>VTK03214</t>
+        </is>
+      </c>
+      <c r="D1274" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Exproof Ekipman Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>KBA-5M Ex-proof Zırhlı Kablo Rakoru, IP66, M50x1.5, Sıkma Aralığı 36-52mm</t>
+        </is>
+      </c>
+      <c r="G1274" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1274" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="J1274" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1274" s="3" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="L1274" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>PROTAŞ PROJE MÜHENDİSLİK (marka: Prosense)</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>VTK03214</t>
+        </is>
+      </c>
+      <c r="D1275" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Exproof Ekipman Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>KBA-1M Ex-proof Zırhlı Kablo Rakoru, IP66, M20x1.5, Sıkma Aralığı 8.5-16mm</t>
+        </is>
+      </c>
+      <c r="G1275" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1275" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J1275" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1275" s="3" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="L1275" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>SETA ÇELİK</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Teklif Konusu: Çelik Tank İmalatı (Rev.1)</t>
+        </is>
+      </c>
+      <c r="D1276" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu - Çelik Tank İmalatı (20.000/7.000/2.000 BBL)</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>20.000 BBL Çelik Tank İmalatı (Ø19000mm H12021mm, S275JR, Dikey Silindirik Atmosferik, Konik Çatı) - İmalat</t>
+        </is>
+      </c>
+      <c r="G1276" s="4" t="n">
+        <v>121587.9</v>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="I1276" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1276" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1276" s="3" t="n">
+        <v>243175.8</v>
+      </c>
+      <c r="L1276" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>SETA ÇELİK</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Teklif Konusu: Çelik Tank İmalatı (Rev.1)</t>
+        </is>
+      </c>
+      <c r="D1277" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu - Çelik Tank İmalatı (20.000/7.000/2.000 BBL)</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>20.000 BBL Çelik Tank Montajı</t>
+        </is>
+      </c>
+      <c r="G1277" s="4" t="n">
+        <v>121587.9</v>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="I1277" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J1277" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1277" s="3" t="n">
+        <v>449875.23</v>
+      </c>
+      <c r="L1277" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>SETA ÇELİK</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Teklif Konusu: Çelik Tank İmalatı (Rev.1)</t>
+        </is>
+      </c>
+      <c r="D1278" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu - Çelik Tank İmalatı (20.000/7.000/2.000 BBL)</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>7.000 BBL Çelik Tank İmalatı (Ø12730mm H8920mm, S275JR, Dikey Silindirik Atmosferik, Konik Çatı) - İmalat</t>
+        </is>
+      </c>
+      <c r="G1278" s="4" t="n">
+        <v>37714.1</v>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="I1278" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1278" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1278" s="3" t="n">
+        <v>75428.2</v>
+      </c>
+      <c r="L1278" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>SETA ÇELİK</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Teklif Konusu: Çelik Tank İmalatı (Rev.1)</t>
+        </is>
+      </c>
+      <c r="D1279" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu - Çelik Tank İmalatı (20.000/7.000/2.000 BBL)</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>7.000 BBL Çelik Tank Montajı</t>
+        </is>
+      </c>
+      <c r="G1279" s="4" t="n">
+        <v>37714.1</v>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="I1279" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J1279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1279" s="3" t="n">
+        <v>139542.17</v>
+      </c>
+      <c r="L1279" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="n">
+        <v>1279</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>SETA ÇELİK</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Teklif Konusu: Çelik Tank İmalatı (Rev.1)</t>
+        </is>
+      </c>
+      <c r="D1280" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu - Çelik Tank İmalatı (20.000/7.000/2.000 BBL)</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>2.000 BBL Çelik Tank İmalatı (Ø7000mm H9000mm, ST52, Dikey Silindirik Atmosferik, Konik Çatı) - İmalat</t>
+        </is>
+      </c>
+      <c r="G1280" s="4" t="n">
+        <v>16046.7</v>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="I1280" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J1280" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1280" s="3" t="n">
+        <v>36907.41</v>
+      </c>
+      <c r="L1280" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="n">
+        <v>1280</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>SETA ÇELİK</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Teklif Konusu: Çelik Tank İmalatı (Rev.1)</t>
+        </is>
+      </c>
+      <c r="D1281" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Mehmet İrfan Güler Petrol Üretim İstasyonu - Çelik Tank İmalatı (20.000/7.000/2.000 BBL)</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>2.000 BBL Çelik Tank Montajı</t>
+        </is>
+      </c>
+      <c r="G1281" s="4" t="n">
+        <v>16046.7</v>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="I1281" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J1281" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1281" s="3" t="n">
+        <v>60977.46</v>
+      </c>
+      <c r="L1281" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="n">
+        <v>1281</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>PATRİON İLERİ TEKNOLOJİ SİSTEMLERİ A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>PK100375</t>
+        </is>
+      </c>
+      <c r="D1282" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Şırnak ADP + Kompanzasyon Pano İmalatı (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>ŞIRNAK ADP Panosu, EAE ES IP55 FORM4B 2000+100x(500+500+400+600+300+600+400)x600mm</t>
+        </is>
+      </c>
+      <c r="G1282" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1282" s="3" t="n">
+        <v>25779.79</v>
+      </c>
+      <c r="J1282" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1282" s="3" t="n">
+        <v>25779.79</v>
+      </c>
+      <c r="L1282" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="n">
+        <v>1282</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>PATRİON İLERİ TEKNOLOJİ SİSTEMLERİ A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>PK100375</t>
+        </is>
+      </c>
+      <c r="D1283" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Şırnak ADP + Kompanzasyon Pano İmalatı (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>ŞIRNAK KOMPANZASYON Panosu, EAE ES IP55 FORM2B 2000+100x(600)x600mm</t>
+        </is>
+      </c>
+      <c r="G1283" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1283" s="3" t="n">
+        <v>3707.79</v>
+      </c>
+      <c r="J1283" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1283" s="3" t="n">
+        <v>3707.79</v>
+      </c>
+      <c r="L1283" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="n">
+        <v>1283</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>YAKAN AYDINLATMA (Selçuk Yakan)</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>003472</t>
+        </is>
+      </c>
+      <c r="D1284" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Kamera Direği Malzemeleri (Alıcı: HB Elektrik - Bayram Çolak)</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>K-95100 Poligon Direk Tek Konsol Galvanizli 10M</t>
+        </is>
+      </c>
+      <c r="G1284" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1284" s="3" t="n">
+        <v>338.25</v>
+      </c>
+      <c r="J1284" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1284" s="3" t="n">
+        <v>6088.5</v>
+      </c>
+      <c r="L1284" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="n">
+        <v>1284</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>YAKAN AYDINLATMA (Selçuk Yakan)</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>003472</t>
+        </is>
+      </c>
+      <c r="D1285" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Kamera Direği Malzemeleri (Alıcı: HB Elektrik - Bayram Çolak)</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>225104 ZEYA 100W 4000K LED Armatür IP66 (ZL-ST22G-100W)</t>
+        </is>
+      </c>
+      <c r="G1285" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1285" s="3" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="J1285" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1285" s="3" t="n">
+        <v>485.1</v>
+      </c>
+      <c r="L1285" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="n">
+        <v>1285</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>YAKAN AYDINLATMA (Selçuk Yakan)</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>003472</t>
+        </is>
+      </c>
+      <c r="D1286" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Kamera Direği Malzemeleri (Alıcı: HB Elektrik - Bayram Çolak)</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>99005 Kamera Direği Çelik Boru 5 Metre</t>
+        </is>
+      </c>
+      <c r="G1286" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1286" s="3" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="J1286" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1286" s="3" t="n">
+        <v>365.13</v>
+      </c>
+      <c r="L1286" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="n">
+        <v>1286</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>YAKAN AYDINLATMA (Selçuk Yakan)</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>003472</t>
+        </is>
+      </c>
+      <c r="D1287" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Kamera Direği Malzemeleri (Alıcı: HB Elektrik - Bayram Çolak)</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>98880 Lazer Kamera Makaralı Konsol Tekli</t>
+        </is>
+      </c>
+      <c r="G1287" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1287" s="3" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="J1287" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1287" s="3" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="L1287" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="n">
+        <v>1287</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>YAKAN AYDINLATMA (Selçuk Yakan)</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>003472</t>
+        </is>
+      </c>
+      <c r="D1288" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Kamera Direği Malzemeleri (Alıcı: HB Elektrik - Bayram Çolak)</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>S01680-1 Galvanizleme (Elektro Galvanizleme)</t>
+        </is>
+      </c>
+      <c r="G1288" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1288" s="3" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J1288" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1288" s="3" t="n">
+        <v>5400</v>
+      </c>
+      <c r="L1288" t="inlineStr">
+        <is>
+          <t>199TPAO_6991374kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1269"/>
+  <autoFilter ref="A1:L1288"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/PROFORMA_FIYAT_LISTESI.xlsx
+++ b/PROFORMA_FIYAT_LISTESI.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Kalem Detay" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1293</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5183,8 +5183,96 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BORUSAN MAKİNA VE GÜÇ SİSTEMLERİ SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ref yok (09.06.2026 Teklif Mektubu)</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Şırnak MİG Petrol Depolama Tesisi - Dizel Jeneratör Seti</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>KDV Hariç. ALTERNATİF (veya): Aynı teklifte CATERPILLAR DE660GC 660KVA Standby (Prime çalışmaya uygun değil) modeli 105.000 EUR KDV Hariç olarak da sunulmuş - iki model birbirinin alternatifi, toplama dahil değil, sadece biri seçilecek. Socomec ATS panosu opsiyoneldir, her iki model için de geçerlidir. Ödeme %30 avans + %70 sevkiyat öncesi.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>199TPAO_13741768kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>MARMARA DİREK AYDINLATMA SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Paratoner/Kamera Direği Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>367920</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Toplam 306.600,00 TL + KDV %20 61.320,00 TL = Genel Toplam 367.920,00 TL. Teslim Yeri İstanbul Fabrika, teslim süresi 4-6 hafta.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>199TPAO_13741768kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J112"/>
+  <autoFilter ref="A1:J114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5195,7 +5283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1288"/>
+  <dimension ref="A1:L1293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -71946,8 +72034,268 @@
         </is>
       </c>
     </row>
+    <row r="1289">
+      <c r="A1289" t="n">
+        <v>1288</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>BORUSAN MAKİNA VE GÜÇ SİSTEMLERİ SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Ref yok (09.06.2026 Teklif Mektubu)</t>
+        </is>
+      </c>
+      <c r="D1289" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Şırnak MİG Petrol Depolama Tesisi - Dizel Jeneratör Seti</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>CATERPILLAR DE660E0 660KVA Standby/600KVA Prime 400V 50Hz 0.8PF 1500RPM Dizel Jeneratör Seti (kontrol paneli, redresör, akü grubu, susturucu, giydirme kabin, alternatör koruma şalteri, nakliye ve devreye alma dahil)</t>
+        </is>
+      </c>
+      <c r="G1289" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1289" s="3" t="n">
+        <v>115000</v>
+      </c>
+      <c r="J1289" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1289" s="3" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L1289" t="inlineStr">
+        <is>
+          <t>199TPAO_13741768kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="n">
+        <v>1289</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>BORUSAN MAKİNA VE GÜÇ SİSTEMLERİ SANAYİ VE TİCARET A.Ş.</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Ref yok (09.06.2026 Teklif Mektubu)</t>
+        </is>
+      </c>
+      <c r="D1290" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Şırnak MİG Petrol Depolama Tesisi - Dizel Jeneratör Seti</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Opsiyonel: Socomec Otomatik Transfer Panosu</t>
+        </is>
+      </c>
+      <c r="G1290" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1290" s="3" t="n">
+        <v>5250</v>
+      </c>
+      <c r="J1290" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K1290" s="3" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L1290" t="inlineStr">
+        <is>
+          <t>199TPAO_13741768kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="n">
+        <v>1290</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>MARMARA DİREK AYDINLATMA SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="D1291" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Paratoner/Kamera Direği Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>10 MT Galvaniz Poligon Aydınlatma Direği Tek Konsol + Tek Kamera Konsollu</t>
+        </is>
+      </c>
+      <c r="G1291" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1291" s="3" t="n">
+        <v>10950</v>
+      </c>
+      <c r="J1291" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1291" s="3" t="n">
+        <v>197100</v>
+      </c>
+      <c r="L1291" t="inlineStr">
+        <is>
+          <t>199TPAO_13741768kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="n">
+        <v>1291</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>MARMARA DİREK AYDINLATMA SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="D1292" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Paratoner/Kamera Direği Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>19 MT Galvaniz Poligon Paratoner Direği</t>
+        </is>
+      </c>
+      <c r="G1292" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1292" s="3" t="n">
+        <v>45750</v>
+      </c>
+      <c r="J1292" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1292" s="3" t="n">
+        <v>91500</v>
+      </c>
+      <c r="L1292" t="inlineStr">
+        <is>
+          <t>199TPAO_13741768kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="n">
+        <v>1292</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>MARMARA DİREK AYDINLATMA SAN. TİC. LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="D1293" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Aydınlatma/Paratoner/Kamera Direği Talebi (Firma: HB Elektrik)</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>5 MT Galvaniz Poligon Kamera Direği</t>
+        </is>
+      </c>
+      <c r="G1293" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="I1293" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="J1293" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="K1293" s="3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L1293" t="inlineStr">
+        <is>
+          <t>199TPAO_13741768kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1288"/>
+  <autoFilter ref="A1:L1293"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/PROFORMA_FIYAT_LISTESI.xlsx
+++ b/PROFORMA_FIYAT_LISTESI.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Kalem Detay" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proforma Özeti'!$A$1:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kalem Detay'!$A$1:$L$1305</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5271,8 +5271,47 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>5052</v>
+      </c>
+      <c r="H115" t="n">
+        <v>12</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Not: TÜRKİYE PETROLLERİ (TPAO); Teklif Formu, Hazırlayan Hasan Ertürk; TOPLAM MİKTAR 1.200,00 m</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J114"/>
+  <autoFilter ref="A1:J115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5283,7 +5322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1293"/>
+  <dimension ref="A1:L1305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -72294,8 +72333,572 @@
         </is>
       </c>
     </row>
+    <row r="1294">
+      <c r="A1294" t="n">
+        <v>1293</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1294" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl 1x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1294" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1294" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J1294" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1294" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="L1294" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="n">
+        <v>1294</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1295" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl-PiMF 2x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1295" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1295" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J1295" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1295" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="L1295" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="n">
+        <v>1295</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1296" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl-PiMF 4x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1296" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1296" s="3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J1296" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1296" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="L1296" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="n">
+        <v>1296</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1297" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl-PiMF 5x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1297" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1297" s="3" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="J1297" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1297" s="3" t="n">
+        <v>477</v>
+      </c>
+      <c r="L1297" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="n">
+        <v>1297</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1298" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl-PiMF 6x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1298" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1298" s="3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="J1298" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1298" s="3" t="n">
+        <v>593</v>
+      </c>
+      <c r="L1298" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="n">
+        <v>1298</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1299" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl-PiMF 8x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1299" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1299" s="3" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="J1299" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1299" s="3" t="n">
+        <v>733</v>
+      </c>
+      <c r="L1299" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="n">
+        <v>1299</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1300" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl-PiMF 10x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1300" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1300" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J1300" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1300" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="L1300" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1301" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>RE-2X(St)YSWAY-fl-PiMF 12x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1301" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1301" s="3" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="J1301" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1301" s="3" t="n">
+        <v>1049</v>
+      </c>
+      <c r="L1301" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1302" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>LI2Y(St)CH 2x2x0.22 mm2 RS-485 (RAL7001-Grey)</t>
+        </is>
+      </c>
+      <c r="G1302" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1302" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J1302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1302" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="L1302" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="n">
+        <v>1302</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1303" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>RE-2Y(St)YSWAY-fl 1x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1303" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1303" s="3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J1303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1303" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="L1303" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1304" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>RE-2Y(St)YSWAY-fl 2x2x1.5 mm2 500V (RAL5015-Blue)</t>
+        </is>
+      </c>
+      <c r="G1304" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1304" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J1304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1304" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="L1304" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>2M KABLO</t>
+        </is>
+      </c>
+      <c r="D1305" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>TÜMAŞ Türk Müh. - TPAO İdil Sahası kablo talebi</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>YSLYCY-OZ 2x1.5 mm2 (RAL7001-Grey)</t>
+        </is>
+      </c>
+      <c r="G1305" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I1305" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J1305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K1305" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L1305" t="inlineStr">
+        <is>
+          <t>1393A_10992064kadar.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1293"/>
+  <autoFilter ref="A1:L1305"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>